--- a/thopen/data/Polaris/Comentários Polaris.xlsx
+++ b/thopen/data/Polaris/Comentários Polaris.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gridcobr.sharepoint.com/sites/GRIDCO/Shared Documents/Gridco/17. Acesso Externo Thopen/3. Polaris/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gridcobr-my.sharepoint.com/personal/levi_maia_gridco_com_br/Documents/Área de Trabalho/temp/Projeto API PV/thopen/data/Polaris/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1508" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF8F47B-CCE9-49A3-A1D3-DE2A9C33B570}"/>
+  <xr:revisionPtr revIDLastSave="1623" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FA92028-3E41-46C8-A56A-E78CA0FF2D9A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C1E55A4-6A58-4802-A746-28D27D2A414B}"/>
   </bookViews>
   <sheets>
     <sheet name="Comentários" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
+    <sheet name="Planilha2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="639">
   <si>
     <t>UFV 1</t>
   </si>
@@ -1439,9 +1440,6 @@
     <t>Usina - Usina Deslgada, Relé Trip 27Abc - 27/06/2026 14:40 às 27/06/2026 21:00</t>
   </si>
   <si>
-    <t>Usina desligada devido falta de pagamento da fatura da concessionaria - de 28/05 até 09/06</t>
-  </si>
-  <si>
     <t>UFV</t>
   </si>
   <si>
@@ -1775,7 +1773,193 @@
     <t>16MIN</t>
   </si>
   <si>
-    <t>Piancó 1</t>
+    <t>Goytacazes</t>
+  </si>
+  <si>
+    <t>Salto do Pirapora</t>
+  </si>
+  <si>
+    <t>Santarém 1A e 1B</t>
+  </si>
+  <si>
+    <t>Ipixuna 1 e 2</t>
+  </si>
+  <si>
+    <t>Piracicaba</t>
+  </si>
+  <si>
+    <t>Aparecida III</t>
+  </si>
+  <si>
+    <t>Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Araçoiaba da Serra IB</t>
+  </si>
+  <si>
+    <t>Araçoiaba da Serra IA e IB</t>
+  </si>
+  <si>
+    <t>Santarém 1A</t>
+  </si>
+  <si>
+    <t>Caxambu I</t>
+  </si>
+  <si>
+    <t>Aparecida do Taboado 1 e 2</t>
+  </si>
+  <si>
+    <t>Vargem Grande</t>
+  </si>
+  <si>
+    <t>Ibaté II</t>
+  </si>
+  <si>
+    <t>Ibaté I</t>
+  </si>
+  <si>
+    <t>Marajoara I</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 47 e 59</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 59N e 67</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 27ABC</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 80 e 81</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 59</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 59N (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 47 e 81 (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 81 (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, devido chave faca da concessionária atuado</t>
+  </si>
+  <si>
+    <t>Usina desligada, por parte da concessionária</t>
+  </si>
+  <si>
+    <t>Usina desligada, devido manutenção programada na rede, por parte da concessionária, trip 27 e 59N</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 47 (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 32 (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, sem proteção/trip ativo</t>
+  </si>
+  <si>
+    <t>Usina ligada, apenas falha de comunicação com o supervisório</t>
+  </si>
+  <si>
+    <t>Inversor Nº 5 em falha/desligado</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé sem trip (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 32, 50, 51 e 67</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé 32 (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Inversor Nº 1 em falha/desligado</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 59N</t>
+  </si>
+  <si>
+    <t>Usina ligada, falha de comunicação devido fibra rompida na região</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 50 e 51</t>
+  </si>
+  <si>
+    <t>Usina ligada, mas em falha de comunicação, devido falta de internet</t>
+  </si>
+  <si>
+    <t>Inversor Nº 2 em falha/desligado</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 27</t>
+  </si>
+  <si>
+    <t>Usina desligada</t>
+  </si>
+  <si>
+    <t>Usina ligada, falha de comunicação com o supervisório</t>
+  </si>
+  <si>
+    <t>Usina desligada, curto no PDE</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 47 (Religado remotamente)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 67</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 50, 51 e 67</t>
+  </si>
+  <si>
+    <t>Manutenção Programada - MPA</t>
+  </si>
+  <si>
+    <t>Inversor nº 6 em falha/desligado</t>
+  </si>
+  <si>
+    <t>Inversor nº 2 ligado, mas em falha de comunicação</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé sem trip (campo) 50 e 51 (supervisório)</t>
+  </si>
+  <si>
+    <t>Inversor nº 8 ligado, mas em falha de comunicação</t>
+  </si>
+  <si>
+    <t>Inversor nº 1 e 2 ligado, mas em falha de comunicação</t>
+  </si>
+  <si>
+    <t>Inversor nº 4, 5, 6 e 14 ligado, mas em falha de comunicação</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé sem trip</t>
+  </si>
+  <si>
+    <t>Inversores nº 4, 5, 6 e 14 em falha de comunicação com o supervisório</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 27ABC e 47</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 32ABC (Religamento remoto)</t>
+  </si>
+  <si>
+    <t>Usina desligada, relé trip 81</t>
+  </si>
+  <si>
+    <t>Usina</t>
+  </si>
+  <si>
+    <t>Cabine</t>
+  </si>
+  <si>
+    <t>Inversor</t>
   </si>
 </sst>
 </file>
@@ -1786,7 +1970,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1827,6 +2011,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1842,7 +2043,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1878,12 +2079,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1972,6 +2186,42 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2008,8 +2258,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9E4F17D-0891-4D97-BD59-CCE6BD4838CF}" name="Tabela6" displayName="Tabela6" ref="B1:D539" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="B1:D539" xr:uid="{CF14C9BA-A6A7-4BFD-A3C9-7EE7822230DB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9E4F17D-0891-4D97-BD59-CCE6BD4838CF}" name="Tabela6" displayName="Tabela6" ref="B1:D629" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="B1:D629" xr:uid="{CF14C9BA-A6A7-4BFD-A3C9-7EE7822230DB}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3840FEB7-BDFC-463D-A309-4251464A7403}" name="UFV 1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{222368D3-AF3F-4BEB-99BE-527F836A68C8}" name="Data" dataDxfId="1"/>
@@ -2319,18 +2569,18 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:D539"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:D629"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="34.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="35.109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="113.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="95.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="14.25" customHeight="1">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2341,7 +2591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2352,7 +2602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2363,7 +2613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4">
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2374,7 +2624,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" ht="28.8">
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2385,7 +2635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:4">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -2396,7 +2646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:4" ht="28.8">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2407,7 +2657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:4">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2418,7 +2668,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4">
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -2427,7 +2677,7 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4">
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2438,7 +2688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2449,7 +2699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:4">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
@@ -2460,7 +2710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:4">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -2482,7 +2732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:4">
       <c r="B15" s="1" t="s">
         <v>22</v>
       </c>
@@ -2493,7 +2743,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:4">
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
@@ -2504,7 +2754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4">
       <c r="B17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2515,7 +2765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4">
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -2526,7 +2776,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:4">
       <c r="B19" s="1" t="s">
         <v>22</v>
       </c>
@@ -2537,7 +2787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
@@ -2548,7 +2798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" ht="28.8">
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
@@ -2559,7 +2809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4">
       <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
@@ -2570,7 +2820,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4">
       <c r="B23" s="1" t="s">
         <v>33</v>
       </c>
@@ -2581,7 +2831,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:4">
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2842,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4">
       <c r="B25" s="1" t="s">
         <v>33</v>
       </c>
@@ -2603,7 +2853,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:4">
       <c r="B26" s="1" t="s">
         <v>37</v>
       </c>
@@ -2614,7 +2864,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:4">
       <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
@@ -2625,7 +2875,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:4">
       <c r="B28" s="1" t="s">
         <v>33</v>
       </c>
@@ -2636,7 +2886,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:4">
       <c r="B29" s="1" t="s">
         <v>37</v>
       </c>
@@ -2647,7 +2897,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:4">
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
@@ -2658,7 +2908,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:4">
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
@@ -2669,7 +2919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:4">
       <c r="B32" s="1" t="s">
         <v>42</v>
       </c>
@@ -2680,7 +2930,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:4">
       <c r="B33" s="1" t="s">
         <v>44</v>
       </c>
@@ -2691,7 +2941,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:4">
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
@@ -2702,7 +2952,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:4">
       <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
@@ -2713,7 +2963,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:4">
       <c r="B36" s="1" t="s">
         <v>18</v>
       </c>
@@ -2724,7 +2974,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:4">
       <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
@@ -2735,7 +2985,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:4">
       <c r="B38" s="1" t="s">
         <v>31</v>
       </c>
@@ -2746,7 +2996,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:4">
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
@@ -2757,7 +3007,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:4">
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
@@ -2768,7 +3018,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:4">
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
@@ -2779,7 +3029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:4">
       <c r="B42" s="1" t="s">
         <v>49</v>
       </c>
@@ -2790,7 +3040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:4">
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
@@ -2801,7 +3051,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:4">
       <c r="B44" s="1" t="s">
         <v>31</v>
       </c>
@@ -2812,7 +3062,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:4">
       <c r="B45" s="1" t="s">
         <v>42</v>
       </c>
@@ -2823,7 +3073,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:4">
       <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
@@ -2834,7 +3084,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:4">
       <c r="B47" s="1" t="s">
         <v>60</v>
       </c>
@@ -2845,7 +3095,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:4">
       <c r="B48" s="1" t="s">
         <v>18</v>
       </c>
@@ -2856,7 +3106,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:4">
       <c r="B49" s="1" t="s">
         <v>13</v>
       </c>
@@ -2867,7 +3117,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:4">
       <c r="B50" s="1" t="s">
         <v>9</v>
       </c>
@@ -2878,7 +3128,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:4">
       <c r="B51" s="1" t="s">
         <v>9</v>
       </c>
@@ -2889,7 +3139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:4">
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
@@ -2900,7 +3150,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:4">
       <c r="B53" s="1" t="s">
         <v>9</v>
       </c>
@@ -2911,7 +3161,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:4">
       <c r="B54" s="1" t="s">
         <v>11</v>
       </c>
@@ -2922,7 +3172,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:4">
       <c r="B55" s="1" t="s">
         <v>3</v>
       </c>
@@ -2933,7 +3183,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:4">
       <c r="B56" s="1" t="s">
         <v>22</v>
       </c>
@@ -2944,7 +3194,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:4">
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
@@ -2955,7 +3205,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:4">
       <c r="B58" s="1" t="s">
         <v>31</v>
       </c>
@@ -2966,7 +3216,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:4">
       <c r="B59" s="1" t="s">
         <v>31</v>
       </c>
@@ -2977,7 +3227,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:4">
       <c r="B60" s="1" t="s">
         <v>42</v>
       </c>
@@ -2988,7 +3238,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:4">
       <c r="B61" s="1" t="s">
         <v>33</v>
       </c>
@@ -2999,7 +3249,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:4">
       <c r="B62" s="1" t="s">
         <v>37</v>
       </c>
@@ -3010,7 +3260,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:4">
       <c r="B63" s="1" t="s">
         <v>11</v>
       </c>
@@ -3021,7 +3271,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:4">
       <c r="B64" s="1" t="s">
         <v>18</v>
       </c>
@@ -3032,7 +3282,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:4">
       <c r="B65" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,7 +3293,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:4">
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
@@ -3054,7 +3304,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:4">
       <c r="B67" s="1" t="s">
         <v>3</v>
       </c>
@@ -3065,7 +3315,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:4">
       <c r="B68" s="1" t="s">
         <v>22</v>
       </c>
@@ -3076,7 +3326,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:4">
       <c r="B69" s="1" t="s">
         <v>49</v>
       </c>
@@ -3087,7 +3337,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:4">
       <c r="B70" s="1" t="s">
         <v>33</v>
       </c>
@@ -3098,7 +3348,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:4">
       <c r="B71" s="1" t="s">
         <v>37</v>
       </c>
@@ -3109,7 +3359,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:4">
       <c r="B72" s="1" t="s">
         <v>11</v>
       </c>
@@ -3120,7 +3370,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:4">
       <c r="B73" s="1" t="s">
         <v>3</v>
       </c>
@@ -3131,7 +3381,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:4">
       <c r="B74" s="1" t="s">
         <v>22</v>
       </c>
@@ -3142,7 +3392,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:4">
       <c r="B75" s="1" t="s">
         <v>60</v>
       </c>
@@ -3153,7 +3403,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:4">
       <c r="B76" s="1" t="s">
         <v>18</v>
       </c>
@@ -3164,7 +3414,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:4">
       <c r="B77" s="1" t="s">
         <v>18</v>
       </c>
@@ -3175,7 +3425,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:4">
       <c r="B78" s="1" t="s">
         <v>13</v>
       </c>
@@ -3186,7 +3436,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:4">
       <c r="B79" s="1" t="s">
         <v>31</v>
       </c>
@@ -3197,7 +3447,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:4">
       <c r="B80" s="1" t="s">
         <v>9</v>
       </c>
@@ -3208,7 +3458,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:4">
       <c r="B81" s="1" t="s">
         <v>18</v>
       </c>
@@ -3219,7 +3469,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:4">
       <c r="B82" s="1" t="s">
         <v>13</v>
       </c>
@@ -3230,7 +3480,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:4">
       <c r="B83" s="1" t="s">
         <v>92</v>
       </c>
@@ -3241,7 +3491,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:4">
       <c r="B84" s="1" t="s">
         <v>31</v>
       </c>
@@ -3252,7 +3502,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:4">
       <c r="B85" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,7 +3513,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:4">
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,7 +3524,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:4">
       <c r="B87" s="1" t="s">
         <v>18</v>
       </c>
@@ -3285,7 +3535,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:4">
       <c r="B88" s="1" t="s">
         <v>25</v>
       </c>
@@ -3296,7 +3546,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:4">
       <c r="B89" s="1" t="s">
         <v>18</v>
       </c>
@@ -3307,7 +3557,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:4">
       <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
@@ -3318,7 +3568,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:4">
       <c r="B91" s="1" t="s">
         <v>5</v>
       </c>
@@ -3329,7 +3579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:4">
       <c r="B92" s="1" t="s">
         <v>92</v>
       </c>
@@ -3340,7 +3590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:4">
       <c r="B93" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,7 +3601,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:4">
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
@@ -3362,7 +3612,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:4">
       <c r="B95" s="1" t="s">
         <v>60</v>
       </c>
@@ -3373,7 +3623,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:4">
       <c r="B96" s="1" t="s">
         <v>3</v>
       </c>
@@ -3384,7 +3634,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:4">
       <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
@@ -3395,7 +3645,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:4">
       <c r="B98" s="1" t="s">
         <v>3</v>
       </c>
@@ -3406,7 +3656,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:4">
       <c r="B99" s="1" t="s">
         <v>22</v>
       </c>
@@ -3417,7 +3667,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:4">
       <c r="B100" s="1" t="s">
         <v>3</v>
       </c>
@@ -3428,7 +3678,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:4">
       <c r="B101" s="1" t="s">
         <v>22</v>
       </c>
@@ -3439,7 +3689,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:4">
       <c r="B102" s="1" t="s">
         <v>22</v>
       </c>
@@ -3450,7 +3700,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:4">
       <c r="B103" s="1" t="s">
         <v>107</v>
       </c>
@@ -3461,7 +3711,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:4">
       <c r="B104" s="1" t="s">
         <v>3</v>
       </c>
@@ -3472,7 +3722,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:4">
       <c r="B105" s="1" t="s">
         <v>22</v>
       </c>
@@ -3483,7 +3733,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="106" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:4" ht="13.2" customHeight="1">
       <c r="B106" s="1" t="s">
         <v>18</v>
       </c>
@@ -3494,7 +3744,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:4">
       <c r="B107" s="1" t="s">
         <v>5</v>
       </c>
@@ -3505,7 +3755,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:4">
       <c r="B108" s="1" t="s">
         <v>92</v>
       </c>
@@ -3516,7 +3766,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:4">
       <c r="B109" s="1" t="s">
         <v>25</v>
       </c>
@@ -3527,7 +3777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:4">
       <c r="B110" s="1" t="s">
         <v>29</v>
       </c>
@@ -3538,7 +3788,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:4">
       <c r="B111" s="1" t="s">
         <v>22</v>
       </c>
@@ -3549,7 +3799,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:4">
       <c r="B112" s="1" t="s">
         <v>18</v>
       </c>
@@ -3560,7 +3810,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:4">
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
@@ -3571,7 +3821,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:4">
       <c r="B114" s="1" t="s">
         <v>31</v>
       </c>
@@ -3582,7 +3832,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:4">
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
@@ -3593,7 +3843,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:4">
       <c r="B116" s="1" t="s">
         <v>33</v>
       </c>
@@ -3604,7 +3854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:4">
       <c r="B117" s="1" t="s">
         <v>60</v>
       </c>
@@ -3615,7 +3865,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:4">
       <c r="B118" s="1" t="s">
         <v>25</v>
       </c>
@@ -3626,7 +3876,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:4">
       <c r="B119" s="1" t="s">
         <v>107</v>
       </c>
@@ -3637,7 +3887,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:4">
       <c r="B120" s="1" t="s">
         <v>31</v>
       </c>
@@ -3648,7 +3898,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:4">
       <c r="B121" s="1" t="s">
         <v>125</v>
       </c>
@@ -3659,7 +3909,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:4">
       <c r="B122" s="1" t="s">
         <v>125</v>
       </c>
@@ -3670,7 +3920,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:4">
       <c r="B123" s="1" t="s">
         <v>128</v>
       </c>
@@ -3681,7 +3931,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:4">
       <c r="B124" s="1" t="s">
         <v>25</v>
       </c>
@@ -3692,7 +3942,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:4">
       <c r="B125" s="1" t="s">
         <v>29</v>
       </c>
@@ -3703,7 +3953,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:4">
       <c r="B126" s="1" t="s">
         <v>128</v>
       </c>
@@ -3714,7 +3964,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:4">
       <c r="B127" s="1" t="s">
         <v>3</v>
       </c>
@@ -3725,7 +3975,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:4">
       <c r="B128" s="1" t="s">
         <v>22</v>
       </c>
@@ -3736,7 +3986,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:4">
       <c r="B129" s="1" t="s">
         <v>33</v>
       </c>
@@ -3747,7 +3997,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:4">
       <c r="B130" s="1" t="s">
         <v>37</v>
       </c>
@@ -3758,7 +4008,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:4">
       <c r="B131" s="1" t="s">
         <v>33</v>
       </c>
@@ -3769,7 +4019,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:4">
       <c r="B132" s="1" t="s">
         <v>37</v>
       </c>
@@ -3780,7 +4030,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:4">
       <c r="B133" s="1" t="s">
         <v>11</v>
       </c>
@@ -3791,7 +4041,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:4">
       <c r="B134" s="1" t="s">
         <v>7</v>
       </c>
@@ -3802,7 +4052,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:4">
       <c r="B135" s="1" t="s">
         <v>138</v>
       </c>
@@ -3813,7 +4063,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:4">
       <c r="B136" s="1" t="s">
         <v>33</v>
       </c>
@@ -3824,7 +4074,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:4">
       <c r="B137" s="1" t="s">
         <v>33</v>
       </c>
@@ -3835,7 +4085,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:4">
       <c r="B138" s="1" t="s">
         <v>37</v>
       </c>
@@ -3846,7 +4096,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:4">
       <c r="B139" s="1" t="s">
         <v>37</v>
       </c>
@@ -3857,7 +4107,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:4">
       <c r="B140" s="1" t="s">
         <v>33</v>
       </c>
@@ -3868,7 +4118,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:4">
       <c r="B141" s="1" t="s">
         <v>37</v>
       </c>
@@ -3879,7 +4129,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:4">
       <c r="B142" s="1" t="s">
         <v>31</v>
       </c>
@@ -3890,7 +4140,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:4">
       <c r="B143" s="1" t="s">
         <v>18</v>
       </c>
@@ -3901,7 +4151,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:4">
       <c r="B144" s="1" t="s">
         <v>125</v>
       </c>
@@ -3912,7 +4162,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:4">
       <c r="B145" s="1" t="s">
         <v>3</v>
       </c>
@@ -3923,7 +4173,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>22</v>
       </c>
@@ -3934,7 +4184,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:4">
       <c r="B147" s="1" t="s">
         <v>18</v>
       </c>
@@ -3945,7 +4195,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:4">
       <c r="B148" s="1" t="s">
         <v>33</v>
       </c>
@@ -3956,7 +4206,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>37</v>
       </c>
@@ -3967,7 +4217,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:4">
       <c r="B150" s="1" t="s">
         <v>125</v>
       </c>
@@ -3978,7 +4228,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:4">
       <c r="B151" s="1" t="s">
         <v>22</v>
       </c>
@@ -3989,7 +4239,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>7</v>
       </c>
@@ -4000,7 +4250,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:4">
       <c r="B153" s="1" t="s">
         <v>33</v>
       </c>
@@ -4011,7 +4261,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>37</v>
       </c>
@@ -4022,7 +4272,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:4">
       <c r="B155" s="1" t="s">
         <v>3</v>
       </c>
@@ -4033,7 +4283,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:4">
       <c r="B156" s="1" t="s">
         <v>22</v>
       </c>
@@ -4044,7 +4294,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>9</v>
       </c>
@@ -4055,7 +4305,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:4">
       <c r="B158" s="1" t="s">
         <v>125</v>
       </c>
@@ -4066,7 +4316,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:4">
       <c r="B159" s="1" t="s">
         <v>3</v>
       </c>
@@ -4077,7 +4327,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:4">
       <c r="B160" s="1" t="s">
         <v>22</v>
       </c>
@@ -4088,7 +4338,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:4">
       <c r="B161" s="1" t="s">
         <v>157</v>
       </c>
@@ -4099,7 +4349,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>13</v>
       </c>
@@ -4110,7 +4360,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:4">
       <c r="B163" s="1" t="s">
         <v>92</v>
       </c>
@@ -4121,7 +4371,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:4">
       <c r="B164" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,7 +4382,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:4">
       <c r="B165" s="1" t="s">
         <v>37</v>
       </c>
@@ -4143,7 +4393,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:4">
       <c r="B166" s="1" t="s">
         <v>3</v>
       </c>
@@ -4154,7 +4404,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:4">
       <c r="B167" s="1" t="s">
         <v>22</v>
       </c>
@@ -4165,7 +4415,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:4">
       <c r="B168" s="1" t="s">
         <v>22</v>
       </c>
@@ -4176,7 +4426,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:4">
       <c r="B169" s="1" t="s">
         <v>107</v>
       </c>
@@ -4187,7 +4437,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>22</v>
       </c>
@@ -4198,7 +4448,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:4">
       <c r="B171" s="1" t="s">
         <v>7</v>
       </c>
@@ -4209,7 +4459,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:4">
       <c r="B172" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,7 +4470,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:4">
       <c r="B173" s="1" t="s">
         <v>3</v>
       </c>
@@ -4231,7 +4481,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:4">
       <c r="B174" s="1" t="s">
         <v>5</v>
       </c>
@@ -4242,7 +4492,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:4">
       <c r="B175" s="1" t="s">
         <v>33</v>
       </c>
@@ -4253,7 +4503,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:4">
       <c r="B176" s="1" t="s">
         <v>107</v>
       </c>
@@ -4264,7 +4514,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:4">
       <c r="B177" s="1" t="s">
         <v>11</v>
       </c>
@@ -4275,7 +4525,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:4">
       <c r="B178" s="1" t="s">
         <v>33</v>
       </c>
@@ -4286,7 +4536,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:4">
       <c r="B179" s="1" t="s">
         <v>5</v>
       </c>
@@ -4297,7 +4547,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:4">
       <c r="B180" s="1" t="s">
         <v>92</v>
       </c>
@@ -4308,7 +4558,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:4">
       <c r="B181" s="1" t="s">
         <v>33</v>
       </c>
@@ -4319,7 +4569,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:4">
       <c r="B182" s="1" t="s">
         <v>33</v>
       </c>
@@ -4330,7 +4580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:4">
       <c r="B183" s="1" t="s">
         <v>5</v>
       </c>
@@ -4341,7 +4591,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:4">
       <c r="B184" s="1" t="s">
         <v>92</v>
       </c>
@@ -4352,7 +4602,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:4">
       <c r="B185" s="1" t="s">
         <v>31</v>
       </c>
@@ -4363,7 +4613,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:4">
       <c r="B186" s="1" t="s">
         <v>33</v>
       </c>
@@ -4374,7 +4624,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="187" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:4" ht="13.95" customHeight="1">
       <c r="B187" s="1" t="s">
         <v>37</v>
       </c>
@@ -4385,7 +4635,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="188" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:4" ht="13.95" customHeight="1">
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
@@ -4396,7 +4646,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="189" spans="2:4" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:4" ht="13.95" customHeight="1">
       <c r="B189" s="1" t="s">
         <v>33</v>
       </c>
@@ -4407,7 +4657,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:4">
       <c r="B190" s="1" t="s">
         <v>33</v>
       </c>
@@ -4418,7 +4668,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:4">
       <c r="B191" s="1" t="s">
         <v>37</v>
       </c>
@@ -4429,7 +4679,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:4">
       <c r="B192" s="1" t="s">
         <v>37</v>
       </c>
@@ -4440,7 +4690,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:4">
       <c r="B193" s="1" t="s">
         <v>25</v>
       </c>
@@ -4451,7 +4701,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:4">
       <c r="B194" s="1" t="s">
         <v>33</v>
       </c>
@@ -4462,7 +4712,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="195" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:4">
       <c r="B195" s="1" t="s">
         <v>33</v>
       </c>
@@ -4473,7 +4723,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="196" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:4">
       <c r="B196" s="1" t="s">
         <v>37</v>
       </c>
@@ -4484,7 +4734,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="197" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:4">
       <c r="B197" s="1" t="s">
         <v>37</v>
       </c>
@@ -4495,7 +4745,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="198" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:4">
       <c r="B198" s="1" t="s">
         <v>60</v>
       </c>
@@ -4506,7 +4756,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="199" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:4">
       <c r="B199" s="1" t="s">
         <v>3</v>
       </c>
@@ -4517,7 +4767,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="200" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:4">
       <c r="B200" s="1" t="s">
         <v>22</v>
       </c>
@@ -4528,7 +4778,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="201" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:4">
       <c r="B201" s="1" t="s">
         <v>31</v>
       </c>
@@ -4539,7 +4789,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="202" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:4">
       <c r="B202" s="1" t="s">
         <v>3</v>
       </c>
@@ -4550,7 +4800,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="203" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:4">
       <c r="B203" s="1" t="s">
         <v>22</v>
       </c>
@@ -4561,7 +4811,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="204" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:4">
       <c r="B204" s="1" t="s">
         <v>33</v>
       </c>
@@ -4572,7 +4822,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="205" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:4">
       <c r="B205" s="1" t="s">
         <v>37</v>
       </c>
@@ -4583,7 +4833,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="206" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:4">
       <c r="B206" s="1" t="s">
         <v>5</v>
       </c>
@@ -4594,7 +4844,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="207" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:4">
       <c r="B207" s="1" t="s">
         <v>33</v>
       </c>
@@ -4605,7 +4855,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="208" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:4">
       <c r="B208" s="1" t="s">
         <v>49</v>
       </c>
@@ -4616,7 +4866,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="209" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:4">
       <c r="B209" s="1" t="s">
         <v>22</v>
       </c>
@@ -4627,7 +4877,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="210" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:4">
       <c r="B210" s="1" t="s">
         <v>3</v>
       </c>
@@ -4638,7 +4888,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="211" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:4">
       <c r="B211" s="1" t="s">
         <v>22</v>
       </c>
@@ -4649,7 +4899,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="212" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:4">
       <c r="B212" s="1" t="s">
         <v>128</v>
       </c>
@@ -4660,7 +4910,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="213" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:4">
       <c r="B213" s="1" t="s">
         <v>9</v>
       </c>
@@ -4671,7 +4921,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="214" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:4">
       <c r="B214" s="1" t="s">
         <v>18</v>
       </c>
@@ -4682,7 +4932,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="215" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:4">
       <c r="B215" s="1" t="s">
         <v>18</v>
       </c>
@@ -4693,7 +4943,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="216" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:4">
       <c r="B216" s="1" t="s">
         <v>22</v>
       </c>
@@ -4704,7 +4954,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="217" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:4">
       <c r="B217" s="1" t="s">
         <v>3</v>
       </c>
@@ -4715,7 +4965,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="218" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:4">
       <c r="B218" s="1" t="s">
         <v>22</v>
       </c>
@@ -4726,7 +4976,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="219" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:4">
       <c r="B219" s="1" t="s">
         <v>3</v>
       </c>
@@ -4737,7 +4987,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="220" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:4">
       <c r="B220" s="1" t="s">
         <v>18</v>
       </c>
@@ -4748,7 +4998,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="221" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:4">
       <c r="B221" s="1" t="s">
         <v>7</v>
       </c>
@@ -4759,7 +5009,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="222" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:4">
       <c r="B222" s="1" t="s">
         <v>33</v>
       </c>
@@ -4770,7 +5020,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="223" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:4">
       <c r="B223" s="1" t="s">
         <v>37</v>
       </c>
@@ -4781,7 +5031,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="224" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:4">
       <c r="B224" s="1" t="s">
         <v>92</v>
       </c>
@@ -4792,7 +5042,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="225" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:4">
       <c r="B225" s="1" t="s">
         <v>3</v>
       </c>
@@ -4803,7 +5053,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="226" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:4">
       <c r="B226" s="1" t="s">
         <v>7</v>
       </c>
@@ -4814,7 +5064,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="227" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:4">
       <c r="B227" s="1" t="s">
         <v>3</v>
       </c>
@@ -4825,7 +5075,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="228" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:4">
       <c r="B228" s="1" t="s">
         <v>5</v>
       </c>
@@ -4836,7 +5086,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="229" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:4">
       <c r="B229" s="1" t="s">
         <v>92</v>
       </c>
@@ -4847,7 +5097,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="230" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:4">
       <c r="B230" s="1" t="s">
         <v>22</v>
       </c>
@@ -4858,7 +5108,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="231" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:4">
       <c r="B231" s="1" t="s">
         <v>3</v>
       </c>
@@ -4869,7 +5119,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="232" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:4">
       <c r="B232" s="1" t="s">
         <v>138</v>
       </c>
@@ -4880,7 +5130,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="233" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:4">
       <c r="B233" s="1" t="s">
         <v>31</v>
       </c>
@@ -4891,7 +5141,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="234" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:4">
       <c r="B234" s="1" t="s">
         <v>33</v>
       </c>
@@ -4902,7 +5152,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="235" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:4">
       <c r="B235" s="1" t="s">
         <v>37</v>
       </c>
@@ -4913,7 +5163,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="236" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:4">
       <c r="B236" s="1" t="s">
         <v>33</v>
       </c>
@@ -4924,7 +5174,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="237" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:4">
       <c r="B237" s="1" t="s">
         <v>49</v>
       </c>
@@ -4935,7 +5185,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="238" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:4">
       <c r="B238" s="1" t="s">
         <v>33</v>
       </c>
@@ -4946,7 +5196,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="239" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:4">
       <c r="B239" s="1" t="s">
         <v>11</v>
       </c>
@@ -4957,7 +5207,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="240" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:4">
       <c r="B240" s="1" t="s">
         <v>33</v>
       </c>
@@ -4968,7 +5218,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="241" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:4">
       <c r="B241" s="1" t="s">
         <v>37</v>
       </c>
@@ -4979,7 +5229,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="242" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:4">
       <c r="B242" s="1" t="s">
         <v>107</v>
       </c>
@@ -4990,7 +5240,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="243" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:4">
       <c r="B243" s="1" t="s">
         <v>125</v>
       </c>
@@ -5001,7 +5251,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="244" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:4">
       <c r="B244" s="1" t="s">
         <v>11</v>
       </c>
@@ -5012,7 +5262,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="245" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:4">
       <c r="B245" s="1" t="s">
         <v>37</v>
       </c>
@@ -5023,7 +5273,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="246" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:4">
       <c r="B246" s="1" t="s">
         <v>11</v>
       </c>
@@ -5034,7 +5284,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="247" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:4">
       <c r="B247" s="1" t="s">
         <v>44</v>
       </c>
@@ -5045,7 +5295,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="248" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:4" ht="13.2" customHeight="1">
       <c r="B248" s="1" t="s">
         <v>33</v>
       </c>
@@ -5056,7 +5306,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="249" spans="2:4" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:4" ht="13.2" customHeight="1">
       <c r="B249" s="1" t="s">
         <v>138</v>
       </c>
@@ -5067,7 +5317,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="250" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:4">
       <c r="B250" s="1" t="s">
         <v>42</v>
       </c>
@@ -5078,7 +5328,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="251" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:4">
       <c r="B251" s="1" t="s">
         <v>33</v>
       </c>
@@ -5089,7 +5339,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="252" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:4">
       <c r="B252" s="1" t="s">
         <v>33</v>
       </c>
@@ -5100,7 +5350,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="253" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:4">
       <c r="B253" s="1" t="s">
         <v>37</v>
       </c>
@@ -5111,7 +5361,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="254" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:4">
       <c r="B254" s="1" t="s">
         <v>125</v>
       </c>
@@ -5122,7 +5372,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="255" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:4">
       <c r="B255" s="1" t="s">
         <v>33</v>
       </c>
@@ -5133,7 +5383,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="256" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:4">
       <c r="B256" s="1" t="s">
         <v>37</v>
       </c>
@@ -5144,7 +5394,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="257" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:4">
       <c r="B257" s="1" t="s">
         <v>9</v>
       </c>
@@ -5155,7 +5405,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="258" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:4">
       <c r="B258" s="1" t="s">
         <v>92</v>
       </c>
@@ -5166,7 +5416,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="259" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:4">
       <c r="B259" s="1" t="s">
         <v>49</v>
       </c>
@@ -5177,7 +5427,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:4">
       <c r="B260" s="1" t="s">
         <v>49</v>
       </c>
@@ -5188,7 +5438,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:4">
       <c r="B261" s="1" t="s">
         <v>22</v>
       </c>
@@ -5199,7 +5449,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="262" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:4">
       <c r="B262" s="1" t="s">
         <v>3</v>
       </c>
@@ -5210,7 +5460,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="263" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:4">
       <c r="B263" s="1" t="s">
         <v>3</v>
       </c>
@@ -5221,7 +5471,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="264" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:4">
       <c r="B264" s="1" t="s">
         <v>42</v>
       </c>
@@ -5232,7 +5482,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="265" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:4">
       <c r="B265" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,7 +5493,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="266" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:4">
       <c r="B266" s="1" t="s">
         <v>31</v>
       </c>
@@ -5254,7 +5504,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="267" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:4">
       <c r="B267" s="1" t="s">
         <v>33</v>
       </c>
@@ -5265,7 +5515,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="268" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:4">
       <c r="B268" s="1" t="s">
         <v>37</v>
       </c>
@@ -5276,7 +5526,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="269" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:4">
       <c r="B269" s="1" t="s">
         <v>44</v>
       </c>
@@ -5287,7 +5537,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="270" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:4">
       <c r="B270" s="1" t="s">
         <v>22</v>
       </c>
@@ -5298,7 +5548,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="271" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:4">
       <c r="B271" s="1" t="s">
         <v>3</v>
       </c>
@@ -5309,7 +5559,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="272" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:4">
       <c r="B272" s="1" t="s">
         <v>49</v>
       </c>
@@ -5320,7 +5570,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="273" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:4">
       <c r="B273" s="1" t="s">
         <v>33</v>
       </c>
@@ -5331,7 +5581,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="274" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:4">
       <c r="B274" s="1" t="s">
         <v>37</v>
       </c>
@@ -5342,7 +5592,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="275" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:4">
       <c r="B275" s="1" t="s">
         <v>31</v>
       </c>
@@ -5353,7 +5603,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="276" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:4">
       <c r="B276" s="1" t="s">
         <v>5</v>
       </c>
@@ -5364,7 +5614,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="277" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:4">
       <c r="B277" s="1" t="s">
         <v>92</v>
       </c>
@@ -5375,7 +5625,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="278" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:4">
       <c r="B278" s="1" t="s">
         <v>31</v>
       </c>
@@ -5386,7 +5636,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="279" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:4">
       <c r="B279" s="1" t="s">
         <v>33</v>
       </c>
@@ -5397,7 +5647,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="280" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:4">
       <c r="B280" s="1" t="s">
         <v>3</v>
       </c>
@@ -5408,7 +5658,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="281" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:4">
       <c r="B281" s="1" t="s">
         <v>22</v>
       </c>
@@ -5419,7 +5669,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="282" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:4">
       <c r="B282" s="1" t="s">
         <v>5</v>
       </c>
@@ -5430,7 +5680,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="283" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:4">
       <c r="B283" s="1" t="s">
         <v>92</v>
       </c>
@@ -5441,7 +5691,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="284" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:4">
       <c r="B284" s="1" t="s">
         <v>107</v>
       </c>
@@ -5452,7 +5702,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="285" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:4">
       <c r="B285" s="1" t="s">
         <v>3</v>
       </c>
@@ -5463,7 +5713,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="286" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:4">
       <c r="B286" s="1" t="s">
         <v>22</v>
       </c>
@@ -5474,7 +5724,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="287" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:4">
       <c r="B287" s="1" t="s">
         <v>128</v>
       </c>
@@ -5485,7 +5735,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="288" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:4">
       <c r="B288" s="1" t="s">
         <v>138</v>
       </c>
@@ -5496,7 +5746,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="289" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:4">
       <c r="B289" s="1" t="s">
         <v>11</v>
       </c>
@@ -5507,7 +5757,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="290" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:4">
       <c r="B290" s="1" t="s">
         <v>125</v>
       </c>
@@ -5518,7 +5768,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="291" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:4">
       <c r="B291" s="1" t="s">
         <v>157</v>
       </c>
@@ -5529,7 +5779,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="292" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:4">
       <c r="B292" s="1" t="s">
         <v>18</v>
       </c>
@@ -5540,7 +5790,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="293" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:4">
       <c r="B293" s="1" t="s">
         <v>128</v>
       </c>
@@ -5551,7 +5801,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="294" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:4">
       <c r="B294" s="1" t="s">
         <v>31</v>
       </c>
@@ -5562,7 +5812,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="295" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:4">
       <c r="B295" s="1" t="s">
         <v>33</v>
       </c>
@@ -5573,7 +5823,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="296" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:4">
       <c r="B296" s="1" t="s">
         <v>37</v>
       </c>
@@ -5584,7 +5834,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="297" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:4">
       <c r="B297" s="1" t="s">
         <v>138</v>
       </c>
@@ -5595,7 +5845,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="298" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:4">
       <c r="B298" s="1" t="s">
         <v>3</v>
       </c>
@@ -5606,7 +5856,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="299" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:4">
       <c r="B299" s="1" t="s">
         <v>22</v>
       </c>
@@ -5617,7 +5867,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="300" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:4">
       <c r="B300" s="1" t="s">
         <v>157</v>
       </c>
@@ -5628,7 +5878,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="301" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:4" ht="28.8">
       <c r="B301" s="1" t="s">
         <v>33</v>
       </c>
@@ -5639,7 +5889,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="302" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:4" ht="28.8">
       <c r="B302" s="1" t="s">
         <v>37</v>
       </c>
@@ -5650,7 +5900,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="303" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:4">
       <c r="B303" s="1" t="s">
         <v>157</v>
       </c>
@@ -5661,7 +5911,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="304" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:4">
       <c r="B304" s="1" t="s">
         <v>13</v>
       </c>
@@ -5672,7 +5922,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="305" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:4">
       <c r="B305" s="1" t="s">
         <v>5</v>
       </c>
@@ -5683,7 +5933,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="306" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:4">
       <c r="B306" s="1" t="s">
         <v>60</v>
       </c>
@@ -5694,7 +5944,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="307" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:4">
       <c r="B307" s="1" t="s">
         <v>13</v>
       </c>
@@ -5705,7 +5955,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="308" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:4">
       <c r="B308" s="1" t="s">
         <v>33</v>
       </c>
@@ -5716,7 +5966,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="309" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:4">
       <c r="B309" s="1" t="s">
         <v>37</v>
       </c>
@@ -5727,7 +5977,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="310" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:4">
       <c r="B310" s="1" t="s">
         <v>18</v>
       </c>
@@ -5738,7 +5988,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="311" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:4">
       <c r="B311" s="1" t="s">
         <v>92</v>
       </c>
@@ -5749,7 +5999,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="312" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:4">
       <c r="B312" s="1" t="s">
         <v>5</v>
       </c>
@@ -5760,7 +6010,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="313" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:4">
       <c r="B313" s="1" t="s">
         <v>92</v>
       </c>
@@ -5771,7 +6021,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="314" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:4">
       <c r="B314" s="1" t="s">
         <v>11</v>
       </c>
@@ -5782,7 +6032,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="315" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:4">
       <c r="B315" s="1" t="s">
         <v>92</v>
       </c>
@@ -5793,7 +6043,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="316" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:4">
       <c r="B316" s="1" t="s">
         <v>31</v>
       </c>
@@ -5804,7 +6054,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="317" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:4">
       <c r="B317" s="1" t="s">
         <v>9</v>
       </c>
@@ -5815,7 +6065,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="318" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:4">
       <c r="B318" s="1" t="s">
         <v>31</v>
       </c>
@@ -5826,7 +6076,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="319" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:4">
       <c r="B319" s="1" t="s">
         <v>125</v>
       </c>
@@ -5837,7 +6087,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="320" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:4">
       <c r="B320" s="1" t="s">
         <v>37</v>
       </c>
@@ -5848,7 +6098,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="321" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:4">
       <c r="B321" s="1" t="s">
         <v>11</v>
       </c>
@@ -5859,7 +6109,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="322" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:4">
       <c r="B322" s="1" t="s">
         <v>31</v>
       </c>
@@ -5870,7 +6120,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="323" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:4">
       <c r="B323" s="1" t="s">
         <v>42</v>
       </c>
@@ -5881,7 +6131,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="324" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:4">
       <c r="B324" s="1" t="s">
         <v>44</v>
       </c>
@@ -5892,7 +6142,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="325" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:4">
       <c r="B325" s="1" t="s">
         <v>33</v>
       </c>
@@ -5903,7 +6153,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="326" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:4">
       <c r="B326" s="1" t="s">
         <v>37</v>
       </c>
@@ -5914,7 +6164,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="327" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:4">
       <c r="B327" s="1" t="s">
         <v>37</v>
       </c>
@@ -5925,7 +6175,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="328" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:4">
       <c r="B328" s="1" t="s">
         <v>13</v>
       </c>
@@ -5936,7 +6186,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="329" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:4" ht="28.8">
       <c r="B329" s="1" t="s">
         <v>138</v>
       </c>
@@ -5947,7 +6197,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="330" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:4">
       <c r="B330" s="1" t="s">
         <v>60</v>
       </c>
@@ -5958,7 +6208,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="331" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:4">
       <c r="B331" s="1" t="s">
         <v>3</v>
       </c>
@@ -5969,7 +6219,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="332" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:4">
       <c r="B332" s="1" t="s">
         <v>33</v>
       </c>
@@ -5980,7 +6230,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="333" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:4">
       <c r="B333" s="1" t="s">
         <v>37</v>
       </c>
@@ -5991,7 +6241,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="334" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:4">
       <c r="B334" s="1" t="s">
         <v>3</v>
       </c>
@@ -6002,7 +6252,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="335" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:4">
       <c r="B335" s="1" t="s">
         <v>22</v>
       </c>
@@ -6013,7 +6263,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="336" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:4">
       <c r="B336" s="1" t="s">
         <v>13</v>
       </c>
@@ -6024,7 +6274,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="337" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:4">
       <c r="B337" s="1" t="s">
         <v>107</v>
       </c>
@@ -6035,7 +6285,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="338" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:4">
       <c r="B338" s="1" t="s">
         <v>11</v>
       </c>
@@ -6046,7 +6296,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="339" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:4">
       <c r="B339" s="1" t="s">
         <v>7</v>
       </c>
@@ -6057,7 +6307,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="340" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:4">
       <c r="B340" s="1" t="s">
         <v>33</v>
       </c>
@@ -6068,7 +6318,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="341" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:4">
       <c r="B341" s="1" t="s">
         <v>37</v>
       </c>
@@ -6079,7 +6329,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="342" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:4">
       <c r="B342" s="1" t="s">
         <v>3</v>
       </c>
@@ -6090,7 +6340,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="343" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:4">
       <c r="B343" s="1" t="s">
         <v>22</v>
       </c>
@@ -6101,7 +6351,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="344" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:4">
       <c r="B344" s="1" t="s">
         <v>7</v>
       </c>
@@ -6112,7 +6362,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="345" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:4">
       <c r="B345" s="1" t="s">
         <v>9</v>
       </c>
@@ -6123,7 +6373,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="346" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:4">
       <c r="B346" s="1" t="s">
         <v>18</v>
       </c>
@@ -6134,7 +6384,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="347" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:4">
       <c r="B347" s="1" t="s">
         <v>7</v>
       </c>
@@ -6145,7 +6395,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="348" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:4">
       <c r="B348" s="1" t="s">
         <v>5</v>
       </c>
@@ -6156,7 +6406,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="349" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:4">
       <c r="B349" s="1" t="s">
         <v>5</v>
       </c>
@@ -6167,7 +6417,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="350" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:4">
       <c r="B350" s="1" t="s">
         <v>5</v>
       </c>
@@ -6178,7 +6428,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="351" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:4">
       <c r="B351" s="1" t="s">
         <v>92</v>
       </c>
@@ -6189,7 +6439,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="352" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:4">
       <c r="B352" s="1" t="s">
         <v>92</v>
       </c>
@@ -6200,7 +6450,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="353" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:4">
       <c r="B353" s="1" t="s">
         <v>92</v>
       </c>
@@ -6211,7 +6461,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="354" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:4">
       <c r="B354" s="1" t="s">
         <v>92</v>
       </c>
@@ -6222,7 +6472,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="355" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:4">
       <c r="B355" s="1" t="s">
         <v>25</v>
       </c>
@@ -6233,7 +6483,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="356" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:4">
       <c r="B356" s="1" t="s">
         <v>25</v>
       </c>
@@ -6244,7 +6494,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="357" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:4">
       <c r="B357" s="1" t="s">
         <v>25</v>
       </c>
@@ -6255,7 +6505,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="358" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:4">
       <c r="B358" s="1" t="s">
         <v>29</v>
       </c>
@@ -6266,7 +6516,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="359" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:4">
       <c r="B359" s="1" t="s">
         <v>29</v>
       </c>
@@ -6277,7 +6527,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="360" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:4">
       <c r="B360" s="1" t="s">
         <v>107</v>
       </c>
@@ -6288,7 +6538,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="361" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:4">
       <c r="B361" s="1" t="s">
         <v>107</v>
       </c>
@@ -6299,7 +6549,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="362" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:4">
       <c r="B362" s="1" t="s">
         <v>31</v>
       </c>
@@ -6310,7 +6560,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="363" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:4">
       <c r="B363" s="1" t="s">
         <v>31</v>
       </c>
@@ -6321,7 +6571,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="364" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:4">
       <c r="B364" s="1" t="s">
         <v>31</v>
       </c>
@@ -6332,7 +6582,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="365" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:4">
       <c r="B365" s="1" t="s">
         <v>31</v>
       </c>
@@ -6343,7 +6593,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="366" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:4">
       <c r="B366" s="1" t="s">
         <v>31</v>
       </c>
@@ -6354,7 +6604,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="367" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:4">
       <c r="B367" s="1" t="s">
         <v>31</v>
       </c>
@@ -6365,7 +6615,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="368" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:4">
       <c r="B368" s="1" t="s">
         <v>31</v>
       </c>
@@ -6376,7 +6626,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="369" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:4">
       <c r="B369" s="1" t="s">
         <v>31</v>
       </c>
@@ -6387,7 +6637,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="370" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:4">
       <c r="B370" s="1" t="s">
         <v>31</v>
       </c>
@@ -6398,7 +6648,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="371" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:4">
       <c r="B371" s="1" t="s">
         <v>31</v>
       </c>
@@ -6409,7 +6659,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="372" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:4">
       <c r="B372" s="1" t="s">
         <v>31</v>
       </c>
@@ -6420,7 +6670,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="373" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:4">
       <c r="B373" s="1" t="s">
         <v>31</v>
       </c>
@@ -6431,7 +6681,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="374" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:4">
       <c r="B374" s="1" t="s">
         <v>337</v>
       </c>
@@ -6442,7 +6692,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="375" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:4">
       <c r="B375" s="1" t="s">
         <v>337</v>
       </c>
@@ -6453,7 +6703,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="376" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:4">
       <c r="B376" s="1" t="s">
         <v>337</v>
       </c>
@@ -6464,7 +6714,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="377" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:4">
       <c r="B377" s="1" t="s">
         <v>341</v>
       </c>
@@ -6475,7 +6725,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="378" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:4">
       <c r="B378" s="1" t="s">
         <v>42</v>
       </c>
@@ -6486,7 +6736,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="379" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:4">
       <c r="B379" s="1" t="s">
         <v>42</v>
       </c>
@@ -6497,7 +6747,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="380" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:4">
       <c r="B380" s="1" t="s">
         <v>42</v>
       </c>
@@ -6508,7 +6758,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="381" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:4">
       <c r="B381" s="1" t="s">
         <v>42</v>
       </c>
@@ -6519,7 +6769,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="382" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:4">
       <c r="B382" s="1" t="s">
         <v>42</v>
       </c>
@@ -6530,7 +6780,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="383" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:4">
       <c r="B383" s="1" t="s">
         <v>44</v>
       </c>
@@ -6541,7 +6791,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="384" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:4">
       <c r="B384" s="1" t="s">
         <v>44</v>
       </c>
@@ -6552,7 +6802,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="385" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:4">
       <c r="B385" s="1" t="s">
         <v>37</v>
       </c>
@@ -6563,7 +6813,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="386" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:4">
       <c r="B386" s="1" t="s">
         <v>33</v>
       </c>
@@ -6574,7 +6824,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="387" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:4">
       <c r="B387" s="1" t="s">
         <v>33</v>
       </c>
@@ -6585,7 +6835,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="388" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:4">
       <c r="B388" s="1" t="s">
         <v>33</v>
       </c>
@@ -6596,7 +6846,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="389" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:4">
       <c r="B389" s="1" t="s">
         <v>33</v>
       </c>
@@ -6607,7 +6857,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:4">
       <c r="B390" s="1" t="s">
         <v>33</v>
       </c>
@@ -6618,7 +6868,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="391" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:4">
       <c r="B391" s="1" t="s">
         <v>33</v>
       </c>
@@ -6629,7 +6879,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="392" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:4">
       <c r="B392" s="1" t="s">
         <v>33</v>
       </c>
@@ -6640,7 +6890,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="393" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:4">
       <c r="B393" s="1" t="s">
         <v>33</v>
       </c>
@@ -6651,7 +6901,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="394" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:4">
       <c r="B394" s="1" t="s">
         <v>33</v>
       </c>
@@ -6662,7 +6912,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="395" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:4">
       <c r="B395" s="1" t="s">
         <v>33</v>
       </c>
@@ -6673,7 +6923,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="396" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:4">
       <c r="B396" s="1" t="s">
         <v>37</v>
       </c>
@@ -6684,7 +6934,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="397" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:4">
       <c r="B397" s="1" t="s">
         <v>37</v>
       </c>
@@ -6695,7 +6945,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="398" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:4">
       <c r="B398" s="1" t="s">
         <v>37</v>
       </c>
@@ -6706,7 +6956,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="399" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:4">
       <c r="B399" s="1" t="s">
         <v>37</v>
       </c>
@@ -6717,7 +6967,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="400" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:4">
       <c r="B400" s="1" t="s">
         <v>37</v>
       </c>
@@ -6728,7 +6978,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="401" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:4">
       <c r="B401" s="1" t="s">
         <v>37</v>
       </c>
@@ -6739,7 +6989,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="402" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:4">
       <c r="B402" s="1" t="s">
         <v>37</v>
       </c>
@@ -6750,7 +7000,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="403" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:4">
       <c r="B403" s="1" t="s">
         <v>37</v>
       </c>
@@ -6761,7 +7011,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="404" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:4">
       <c r="B404" s="1" t="s">
         <v>37</v>
       </c>
@@ -6772,7 +7022,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="405" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:4">
       <c r="B405" s="1" t="s">
         <v>125</v>
       </c>
@@ -6783,7 +7033,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="406" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:4">
       <c r="B406" s="1" t="s">
         <v>11</v>
       </c>
@@ -6794,7 +7044,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="407" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:4">
       <c r="B407" s="1" t="s">
         <v>11</v>
       </c>
@@ -6805,7 +7055,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="408" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:4">
       <c r="B408" s="1" t="s">
         <v>11</v>
       </c>
@@ -6816,7 +7066,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="409" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:4">
       <c r="B409" s="1" t="s">
         <v>11</v>
       </c>
@@ -6827,7 +7077,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="410" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:4">
       <c r="B410" s="1" t="s">
         <v>3</v>
       </c>
@@ -6838,7 +7088,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="411" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:4">
       <c r="B411" s="1" t="s">
         <v>3</v>
       </c>
@@ -6849,7 +7099,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="412" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:4">
       <c r="B412" s="1" t="s">
         <v>3</v>
       </c>
@@ -6860,7 +7110,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="413" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:4">
       <c r="B413" s="1" t="s">
         <v>3</v>
       </c>
@@ -6871,7 +7121,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="414" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:4">
       <c r="B414" s="1" t="s">
         <v>3</v>
       </c>
@@ -6882,7 +7132,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="415" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:4">
       <c r="B415" s="1" t="s">
         <v>3</v>
       </c>
@@ -6893,7 +7143,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="416" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:4">
       <c r="B416" s="1" t="s">
         <v>3</v>
       </c>
@@ -6904,7 +7154,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="417" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:4">
       <c r="B417" s="1" t="s">
         <v>3</v>
       </c>
@@ -6915,7 +7165,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="418" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:4">
       <c r="B418" s="1" t="s">
         <v>3</v>
       </c>
@@ -6926,7 +7176,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="419" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:4">
       <c r="B419" s="1" t="s">
         <v>22</v>
       </c>
@@ -6937,7 +7187,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="420" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:4">
       <c r="B420" s="1" t="s">
         <v>22</v>
       </c>
@@ -6948,7 +7198,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="421" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:4">
       <c r="B421" s="1" t="s">
         <v>22</v>
       </c>
@@ -6959,7 +7209,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="422" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:4">
       <c r="B422" s="1" t="s">
         <v>22</v>
       </c>
@@ -6970,7 +7220,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="423" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:4">
       <c r="B423" s="1" t="s">
         <v>22</v>
       </c>
@@ -6981,7 +7231,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="424" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:4">
       <c r="B424" s="1" t="s">
         <v>22</v>
       </c>
@@ -6992,7 +7242,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="425" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:4">
       <c r="B425" s="1" t="s">
         <v>18</v>
       </c>
@@ -7003,7 +7253,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="426" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:4">
       <c r="B426" s="1" t="s">
         <v>18</v>
       </c>
@@ -7014,7 +7264,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="427" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:4">
       <c r="B427" s="1" t="s">
         <v>379</v>
       </c>
@@ -7025,7 +7275,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="428" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:4">
       <c r="B428" s="1" t="s">
         <v>379</v>
       </c>
@@ -7036,7 +7286,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="429" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:4">
       <c r="B429" s="1" t="s">
         <v>379</v>
       </c>
@@ -7047,7 +7297,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="430" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:4">
       <c r="B430" s="1" t="s">
         <v>379</v>
       </c>
@@ -7058,7 +7308,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="431" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:4">
       <c r="B431" s="1" t="s">
         <v>379</v>
       </c>
@@ -7069,7 +7319,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="432" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:4">
       <c r="B432" s="1" t="s">
         <v>128</v>
       </c>
@@ -7080,7 +7330,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="433" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:4">
       <c r="B433" s="1" t="s">
         <v>128</v>
       </c>
@@ -7091,7 +7341,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="434" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:4">
       <c r="B434" s="1" t="s">
         <v>128</v>
       </c>
@@ -7102,7 +7352,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="435" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:4">
       <c r="B435" s="1" t="s">
         <v>128</v>
       </c>
@@ -7113,7 +7363,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="436" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:4">
       <c r="B436" s="1" t="s">
         <v>42</v>
       </c>
@@ -7124,7 +7374,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="437" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:4">
       <c r="B437" s="1" t="s">
         <v>33</v>
       </c>
@@ -7135,7 +7385,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="438" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:4">
       <c r="B438" s="1" t="s">
         <v>37</v>
       </c>
@@ -7146,7 +7396,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="439" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:4">
       <c r="B439" s="1" t="s">
         <v>33</v>
       </c>
@@ -7157,7 +7407,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="440" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:4">
       <c r="B440" s="1" t="s">
         <v>37</v>
       </c>
@@ -7168,7 +7418,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="441" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:4">
       <c r="B441" s="1" t="s">
         <v>31</v>
       </c>
@@ -7179,7 +7429,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="442" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:4">
       <c r="B442" s="1" t="s">
         <v>337</v>
       </c>
@@ -7190,7 +7440,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="443" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:4">
       <c r="B443" s="1" t="s">
         <v>37</v>
       </c>
@@ -7201,7 +7451,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="444" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:4">
       <c r="B444" s="1" t="s">
         <v>33</v>
       </c>
@@ -7212,7 +7462,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="445" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:4">
       <c r="B445" s="1" t="s">
         <v>37</v>
       </c>
@@ -7223,7 +7473,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="446" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:4">
       <c r="B446" s="1" t="s">
         <v>33</v>
       </c>
@@ -7234,7 +7484,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="447" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:4">
       <c r="B447" s="1" t="s">
         <v>37</v>
       </c>
@@ -7245,7 +7495,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="448" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:4">
       <c r="B448" s="1" t="s">
         <v>31</v>
       </c>
@@ -7256,7 +7506,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="449" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:4">
       <c r="B449" s="1" t="s">
         <v>42</v>
       </c>
@@ -7267,7 +7517,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="450" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:4">
       <c r="B450" s="1" t="s">
         <v>25</v>
       </c>
@@ -7278,7 +7528,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="451" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:4">
       <c r="B451" s="1" t="s">
         <v>7</v>
       </c>
@@ -7289,7 +7539,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="452" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:4">
       <c r="B452" s="1" t="s">
         <v>125</v>
       </c>
@@ -7300,7 +7550,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="453" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:4">
       <c r="B453" s="1" t="s">
         <v>125</v>
       </c>
@@ -7311,7 +7561,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="454" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:4">
       <c r="B454" s="1" t="s">
         <v>33</v>
       </c>
@@ -7322,7 +7572,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="455" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:4">
       <c r="B455" s="1" t="s">
         <v>37</v>
       </c>
@@ -7333,7 +7583,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="456" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:4">
       <c r="B456" s="1" t="s">
         <v>33</v>
       </c>
@@ -7344,7 +7594,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="457" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:4">
       <c r="B457" s="1" t="s">
         <v>37</v>
       </c>
@@ -7355,7 +7605,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="458" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:4">
       <c r="B458" s="1" t="s">
         <v>379</v>
       </c>
@@ -7366,7 +7616,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="459" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:4">
       <c r="B459" s="1" t="s">
         <v>33</v>
       </c>
@@ -7377,7 +7627,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="460" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:4">
       <c r="B460" s="1" t="s">
         <v>37</v>
       </c>
@@ -7388,7 +7638,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="461" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:4">
       <c r="B461" s="1" t="s">
         <v>22</v>
       </c>
@@ -7399,7 +7649,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="462" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:4">
       <c r="B462" s="1" t="s">
         <v>25</v>
       </c>
@@ -7410,7 +7660,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="463" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:4">
       <c r="B463" s="1" t="s">
         <v>33</v>
       </c>
@@ -7421,7 +7671,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="464" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:4">
       <c r="B464" s="1" t="s">
         <v>37</v>
       </c>
@@ -7432,7 +7682,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="465" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:4">
       <c r="B465" s="1" t="s">
         <v>3</v>
       </c>
@@ -7443,7 +7693,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="466" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:4">
       <c r="B466" s="1" t="s">
         <v>31</v>
       </c>
@@ -7454,7 +7704,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="467" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:4">
       <c r="B467" s="1" t="s">
         <v>7</v>
       </c>
@@ -7465,7 +7715,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="468" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:4">
       <c r="B468" s="1" t="s">
         <v>3</v>
       </c>
@@ -7476,7 +7726,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="469" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:4">
       <c r="B469" s="1" t="s">
         <v>22</v>
       </c>
@@ -7487,7 +7737,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="470" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:4">
       <c r="B470" s="1" t="s">
         <v>379</v>
       </c>
@@ -7498,7 +7748,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="471" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:4">
       <c r="B471" s="1" t="s">
         <v>337</v>
       </c>
@@ -7509,7 +7759,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="472" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:4">
       <c r="B472" s="1" t="s">
         <v>7</v>
       </c>
@@ -7520,7 +7770,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="473" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:4">
       <c r="B473" s="1" t="s">
         <v>31</v>
       </c>
@@ -7531,7 +7781,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="474" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:4">
       <c r="B474" s="1" t="s">
         <v>33</v>
       </c>
@@ -7542,7 +7792,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="475" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:4">
       <c r="B475" s="1" t="s">
         <v>37</v>
       </c>
@@ -7553,7 +7803,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="476" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:4">
       <c r="B476" s="1" t="s">
         <v>33</v>
       </c>
@@ -7564,7 +7814,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="477" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:4">
       <c r="B477" s="1" t="s">
         <v>37</v>
       </c>
@@ -7575,7 +7825,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="478" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:4">
       <c r="B478" s="1" t="s">
         <v>128</v>
       </c>
@@ -7586,7 +7836,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="479" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:4">
       <c r="B479" s="1" t="s">
         <v>42</v>
       </c>
@@ -7597,7 +7847,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="480" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:4">
       <c r="B480" s="1" t="s">
         <v>33</v>
       </c>
@@ -7608,7 +7858,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="481" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:4">
       <c r="B481" s="1" t="s">
         <v>31</v>
       </c>
@@ -7619,7 +7869,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="482" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:4">
       <c r="B482" s="1" t="s">
         <v>42</v>
       </c>
@@ -7630,7 +7880,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="483" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:4">
       <c r="B483" s="1" t="s">
         <v>44</v>
       </c>
@@ -7641,7 +7891,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="484" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:4">
       <c r="B484" s="1" t="s">
         <v>37</v>
       </c>
@@ -7652,7 +7902,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="485" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:4">
       <c r="B485" s="1" t="s">
         <v>42</v>
       </c>
@@ -7663,7 +7913,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="486" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:4">
       <c r="B486" s="1" t="s">
         <v>42</v>
       </c>
@@ -7674,7 +7924,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="487" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:4">
       <c r="B487" s="1" t="s">
         <v>44</v>
       </c>
@@ -7685,7 +7935,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="488" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:4">
       <c r="B488" s="1" t="s">
         <v>25</v>
       </c>
@@ -7696,7 +7946,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="489" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:4">
       <c r="B489" s="1" t="s">
         <v>33</v>
       </c>
@@ -7707,7 +7957,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="490" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:4">
       <c r="B490" s="1" t="s">
         <v>37</v>
       </c>
@@ -7718,7 +7968,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="491" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:4">
       <c r="B491" s="1" t="s">
         <v>5</v>
       </c>
@@ -7729,7 +7979,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="492" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:4">
       <c r="B492" s="1" t="s">
         <v>92</v>
       </c>
@@ -7740,7 +7990,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="493" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:4">
       <c r="B493" s="1" t="s">
         <v>31</v>
       </c>
@@ -7751,7 +8001,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="494" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:4">
       <c r="B494" s="1" t="s">
         <v>5</v>
       </c>
@@ -7762,7 +8012,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="495" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:4">
       <c r="B495" s="1" t="s">
         <v>92</v>
       </c>
@@ -7773,7 +8023,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="496" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:4">
       <c r="B496" s="1" t="s">
         <v>379</v>
       </c>
@@ -7784,7 +8034,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="497" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:4">
       <c r="B497" s="1" t="s">
         <v>33</v>
       </c>
@@ -7795,7 +8045,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="498" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:4">
       <c r="B498" s="1" t="s">
         <v>37</v>
       </c>
@@ -7806,7 +8056,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="499" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:4">
       <c r="B499" s="1" t="s">
         <v>3</v>
       </c>
@@ -7817,7 +8067,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="500" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:4">
       <c r="B500" s="1" t="s">
         <v>22</v>
       </c>
@@ -7828,7 +8078,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="501" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:4">
       <c r="B501" s="1" t="s">
         <v>44</v>
       </c>
@@ -7839,7 +8089,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="502" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:4">
       <c r="B502" s="1" t="s">
         <v>33</v>
       </c>
@@ -7850,7 +8100,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="503" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:4">
       <c r="B503" s="1" t="s">
         <v>31</v>
       </c>
@@ -7861,7 +8111,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="504" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:4">
       <c r="B504" s="1" t="s">
         <v>31</v>
       </c>
@@ -7872,7 +8122,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="505" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:4">
       <c r="B505" s="1" t="s">
         <v>42</v>
       </c>
@@ -7883,7 +8133,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="506" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:4">
       <c r="B506" s="1" t="s">
         <v>31</v>
       </c>
@@ -7894,7 +8144,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="507" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:4">
       <c r="B507" s="1" t="s">
         <v>379</v>
       </c>
@@ -7905,7 +8155,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="508" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:4">
       <c r="B508" s="1" t="s">
         <v>33</v>
       </c>
@@ -7916,7 +8166,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="509" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:4">
       <c r="B509" s="1" t="s">
         <v>37</v>
       </c>
@@ -7927,7 +8177,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="510" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:4">
       <c r="B510" s="1" t="s">
         <v>33</v>
       </c>
@@ -7938,7 +8188,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="511" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:4">
       <c r="B511" s="1" t="s">
         <v>37</v>
       </c>
@@ -7949,7 +8199,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="512" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:4">
       <c r="B512" s="1" t="s">
         <v>33</v>
       </c>
@@ -7960,7 +8210,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="513" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:4">
       <c r="B513" s="1" t="s">
         <v>37</v>
       </c>
@@ -7971,7 +8221,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="514" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:4">
       <c r="B514" s="1" t="s">
         <v>37</v>
       </c>
@@ -7982,7 +8232,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="515" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:4">
       <c r="B515" s="1" t="s">
         <v>3</v>
       </c>
@@ -7993,7 +8243,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="516" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:4">
       <c r="B516" s="1" t="s">
         <v>128</v>
       </c>
@@ -8004,7 +8254,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="517" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:4">
       <c r="B517" s="1" t="s">
         <v>33</v>
       </c>
@@ -8015,7 +8265,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="518" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:4">
       <c r="B518" s="1" t="s">
         <v>37</v>
       </c>
@@ -8026,7 +8276,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="519" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:4">
       <c r="B519" s="1" t="s">
         <v>33</v>
       </c>
@@ -8037,7 +8287,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="520" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:4">
       <c r="B520" s="1" t="s">
         <v>37</v>
       </c>
@@ -8048,7 +8298,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="521" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:4">
       <c r="B521" s="1" t="s">
         <v>42</v>
       </c>
@@ -8059,7 +8309,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="522" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:4">
       <c r="B522" s="1" t="s">
         <v>33</v>
       </c>
@@ -8070,7 +8320,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="523" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:4">
       <c r="B523" s="1" t="s">
         <v>37</v>
       </c>
@@ -8081,7 +8331,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="524" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:4">
       <c r="B524" s="1" t="s">
         <v>33</v>
       </c>
@@ -8092,7 +8342,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="525" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:4">
       <c r="B525" s="1" t="s">
         <v>37</v>
       </c>
@@ -8103,7 +8353,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="526" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:4">
       <c r="B526" s="1" t="s">
         <v>44</v>
       </c>
@@ -8114,7 +8364,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="527" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:4">
       <c r="B527" s="1" t="s">
         <v>42</v>
       </c>
@@ -8125,7 +8375,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="528" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:4">
       <c r="B528" s="1" t="s">
         <v>31</v>
       </c>
@@ -8136,7 +8386,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="529" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:4">
       <c r="B529" s="1" t="s">
         <v>11</v>
       </c>
@@ -8147,7 +8397,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="530" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:4">
       <c r="B530" s="1" t="s">
         <v>33</v>
       </c>
@@ -8158,7 +8408,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="531" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:4">
       <c r="B531" s="1" t="s">
         <v>37</v>
       </c>
@@ -8169,7 +8419,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="532" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:4">
       <c r="B532" s="1" t="s">
         <v>44</v>
       </c>
@@ -8180,7 +8430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="533" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:4">
       <c r="B533" s="1" t="s">
         <v>157</v>
       </c>
@@ -8191,7 +8441,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="534" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:4">
       <c r="B534" s="1" t="s">
         <v>13</v>
       </c>
@@ -8202,7 +8452,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="535" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:4">
       <c r="B535" s="1" t="s">
         <v>33</v>
       </c>
@@ -8213,7 +8463,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="536" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:4">
       <c r="B536" s="1" t="s">
         <v>37</v>
       </c>
@@ -8224,7 +8474,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="537" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:4">
       <c r="B537" s="1" t="s">
         <v>33</v>
       </c>
@@ -8235,7 +8485,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="538" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:4">
       <c r="B538" s="1" t="s">
         <v>37</v>
       </c>
@@ -8246,15 +8496,1005 @@
         <v>464</v>
       </c>
     </row>
-    <row r="539" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:4">
       <c r="B539" s="1" t="s">
-        <v>577</v>
+        <v>31</v>
       </c>
       <c r="C539" s="3">
-        <v>46174</v>
-      </c>
-      <c r="D539" s="29" t="s">
-        <v>465</v>
+        <v>46237.208333333336</v>
+      </c>
+      <c r="D539" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="540" spans="2:4">
+      <c r="B540" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C540" s="3">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="D540" s="6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="541" spans="2:4">
+      <c r="B541" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C541" s="3">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="D541" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="542" spans="2:4">
+      <c r="B542" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C542" s="3">
+        <v>46237.40625</v>
+      </c>
+      <c r="D542" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="543" spans="2:4">
+      <c r="B543" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C543" s="3">
+        <v>46237.434027777781</v>
+      </c>
+      <c r="D543" s="6" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="544" spans="2:4">
+      <c r="B544" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C544" s="3">
+        <v>46237.749305555553</v>
+      </c>
+      <c r="D544" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="545" spans="2:4">
+      <c r="B545" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C545" s="3">
+        <v>46238.28402777778</v>
+      </c>
+      <c r="D545" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="546" spans="2:4">
+      <c r="B546" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C546" s="3">
+        <v>46238.28402777778</v>
+      </c>
+      <c r="D546" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="547" spans="2:4">
+      <c r="B547" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C547" s="3">
+        <v>46238.325694444444</v>
+      </c>
+      <c r="D547" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="548" spans="2:4">
+      <c r="B548" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C548" s="3">
+        <v>46238.325694444444</v>
+      </c>
+      <c r="D548" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="549" spans="2:4">
+      <c r="B549" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C549" s="3">
+        <v>46238.571527777778</v>
+      </c>
+      <c r="D549" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="550" spans="2:4">
+      <c r="B550" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C550" s="3">
+        <v>46239.586805555555</v>
+      </c>
+      <c r="D550" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="551" spans="2:4">
+      <c r="B551" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C551" s="3">
+        <v>46240.491666666669</v>
+      </c>
+      <c r="D551" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="552" spans="2:4">
+      <c r="B552" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C552" s="3">
+        <v>46240.517361111109</v>
+      </c>
+      <c r="D552" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="553" spans="2:4">
+      <c r="B553" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C553" s="3">
+        <v>46241.340277777781</v>
+      </c>
+      <c r="D553" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="554" spans="2:4">
+      <c r="B554" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C554" s="3">
+        <v>46241.416666666664</v>
+      </c>
+      <c r="D554" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="555" spans="2:4">
+      <c r="B555" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C555" s="3">
+        <v>46241.51458333333</v>
+      </c>
+      <c r="D555" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="556" spans="2:4">
+      <c r="B556" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C556" s="3">
+        <v>46241.670138888891</v>
+      </c>
+      <c r="D556" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="557" spans="2:4">
+      <c r="B557" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C557" s="3">
+        <v>46242.579861111109</v>
+      </c>
+      <c r="D557" s="6" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="558" spans="2:4">
+      <c r="B558" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C558" s="3">
+        <v>46242.729166666664</v>
+      </c>
+      <c r="D558" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="559" spans="2:4">
+      <c r="B559" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C559" s="3">
+        <v>46242.729166666664</v>
+      </c>
+      <c r="D559" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="560" spans="2:4">
+      <c r="B560" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C560" s="3">
+        <v>46242.759027777778</v>
+      </c>
+      <c r="D560" s="6" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="561" spans="2:4">
+      <c r="B561" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C561" s="3">
+        <v>46243.291666666664</v>
+      </c>
+      <c r="D561" s="6" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="562" spans="2:4">
+      <c r="B562" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C562" s="3">
+        <v>46243.614583333336</v>
+      </c>
+      <c r="D562" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="563" spans="2:4">
+      <c r="B563" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C563" s="3">
+        <v>46243.642361111109</v>
+      </c>
+      <c r="D563" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="564" spans="2:4">
+      <c r="B564" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C564" s="3">
+        <v>46243.942361111112</v>
+      </c>
+      <c r="D564" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="565" spans="2:4">
+      <c r="B565" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C565" s="3">
+        <v>46243.942361111112</v>
+      </c>
+      <c r="D565" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="566" spans="2:4">
+      <c r="B566" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C566" s="3">
+        <v>46244.413194444445</v>
+      </c>
+      <c r="D566" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="567" spans="2:4">
+      <c r="B567" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C567" s="3">
+        <v>46244.413194444445</v>
+      </c>
+      <c r="D567" s="6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="568" spans="2:4">
+      <c r="B568" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C568" s="3">
+        <v>46244.951388888891</v>
+      </c>
+      <c r="D568" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="569" spans="2:4">
+      <c r="B569" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C569" s="3">
+        <v>46245.40625</v>
+      </c>
+      <c r="D569" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="570" spans="2:4">
+      <c r="B570" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C570" s="3">
+        <v>46245.479166666664</v>
+      </c>
+      <c r="D570" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="571" spans="2:4">
+      <c r="B571" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C571" s="3">
+        <v>46245.522222222222</v>
+      </c>
+      <c r="D571" s="6" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="572" spans="2:4">
+      <c r="B572" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C572" s="3">
+        <v>46247.347222222219</v>
+      </c>
+      <c r="D572" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="573" spans="2:4">
+      <c r="B573" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C573" s="3">
+        <v>46247.347222222219</v>
+      </c>
+      <c r="D573" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="574" spans="2:4">
+      <c r="B574" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C574" s="3">
+        <v>46247.440972222219</v>
+      </c>
+      <c r="D574" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="575" spans="2:4">
+      <c r="B575" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C575" s="3">
+        <v>46248.30972222222</v>
+      </c>
+      <c r="D575" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="576" spans="2:4">
+      <c r="B576" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C576" s="3">
+        <v>46249.361111111109</v>
+      </c>
+      <c r="D576" s="6" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="577" spans="2:4">
+      <c r="B577" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C577" s="3">
+        <v>46249.607638888891</v>
+      </c>
+      <c r="D577" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="578" spans="2:4">
+      <c r="B578" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C578" s="3">
+        <v>46250.541666666664</v>
+      </c>
+      <c r="D578" s="6" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="579" spans="2:4">
+      <c r="B579" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C579" s="3">
+        <v>46252.458333333336</v>
+      </c>
+      <c r="D579" s="6" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="580" spans="2:4">
+      <c r="B580" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C580" s="3">
+        <v>46252.460416666669</v>
+      </c>
+      <c r="D580" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="581" spans="2:4">
+      <c r="B581" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C581" s="3">
+        <v>46252.460416666669</v>
+      </c>
+      <c r="D581" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="582" spans="2:4">
+      <c r="B582" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C582" s="3">
+        <v>46252.552083333336</v>
+      </c>
+      <c r="D582" s="6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="583" spans="2:4">
+      <c r="B583" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C583" s="3">
+        <v>46253.229166666664</v>
+      </c>
+      <c r="D583" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="584" spans="2:4">
+      <c r="B584" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C584" s="3">
+        <v>46253.447916666664</v>
+      </c>
+      <c r="D584" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="585" spans="2:4">
+      <c r="B585" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C585" s="3">
+        <v>46253.447916666664</v>
+      </c>
+      <c r="D585" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="586" spans="2:4">
+      <c r="B586" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C586" s="3">
+        <v>46253.583333333336</v>
+      </c>
+      <c r="D586" s="6" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="587" spans="2:4">
+      <c r="B587" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C587" s="3">
+        <v>46254.427083333336</v>
+      </c>
+      <c r="D587" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="588" spans="2:4">
+      <c r="B588" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C588" s="3">
+        <v>46254.576388888891</v>
+      </c>
+      <c r="D588" s="6" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="589" spans="2:4">
+      <c r="B589" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C589" s="3">
+        <v>46254.708333333336</v>
+      </c>
+      <c r="D589" s="6" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="590" spans="2:4">
+      <c r="B590" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C590" s="3">
+        <v>46255.3125</v>
+      </c>
+      <c r="D590" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="591" spans="2:4">
+      <c r="B591" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C591" s="3">
+        <v>46255.548611111109</v>
+      </c>
+      <c r="D591" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="592" spans="2:4">
+      <c r="B592" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C592" s="3">
+        <v>46256.088194444441</v>
+      </c>
+      <c r="D592" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="593" spans="2:4">
+      <c r="B593" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C593" s="3">
+        <v>46256.394444444442</v>
+      </c>
+      <c r="D593" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="594" spans="2:4">
+      <c r="B594" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C594" s="3">
+        <v>46257.40347222222</v>
+      </c>
+      <c r="D594" s="6" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="595" spans="2:4">
+      <c r="B595" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C595" s="3">
+        <v>46257.40347222222</v>
+      </c>
+      <c r="D595" s="6" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="596" spans="2:4">
+      <c r="B596" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C596" s="3">
+        <v>46257.534722222219</v>
+      </c>
+      <c r="D596" s="6" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="597" spans="2:4">
+      <c r="B597" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C597" s="3">
+        <v>46257.638888888891</v>
+      </c>
+      <c r="D597" s="6" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="598" spans="2:4">
+      <c r="B598" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C598" s="3">
+        <v>46257.913888888892</v>
+      </c>
+      <c r="D598" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="599" spans="2:4">
+      <c r="B599" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C599" s="3">
+        <v>46257.913888888892</v>
+      </c>
+      <c r="D599" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="600" spans="2:4">
+      <c r="B600" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C600" s="3">
+        <v>46258.494664351849</v>
+      </c>
+      <c r="D600" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="601" spans="2:4">
+      <c r="B601" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C601" s="3">
+        <v>46259.371527777781</v>
+      </c>
+      <c r="D601" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="602" spans="2:4">
+      <c r="B602" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C602" s="3">
+        <v>46259.390972222223</v>
+      </c>
+      <c r="D602" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="603" spans="2:4">
+      <c r="B603" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C603" s="3">
+        <v>46259.545138888891</v>
+      </c>
+      <c r="D603" s="6" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="604" spans="2:4">
+      <c r="B604" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C604" s="3">
+        <v>46259.5625</v>
+      </c>
+      <c r="D604" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="605" spans="2:4">
+      <c r="B605" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C605" s="3">
+        <v>46259.5625</v>
+      </c>
+      <c r="D605" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="606" spans="2:4">
+      <c r="B606" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C606" s="3">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="D606" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="607" spans="2:4">
+      <c r="B607" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C607" s="3">
+        <v>46261.262499999997</v>
+      </c>
+      <c r="D607" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="608" spans="2:4">
+      <c r="B608" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C608" s="3">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="D608" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="609" spans="2:4">
+      <c r="B609" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C609" s="3">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="D609" s="6" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="610" spans="2:4">
+      <c r="B610" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C610" s="3">
+        <v>46261.340277777781</v>
+      </c>
+      <c r="D610" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="611" spans="2:4">
+      <c r="B611" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C611" s="3">
+        <v>46261.444444444445</v>
+      </c>
+      <c r="D611" s="6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="612" spans="2:4">
+      <c r="B612" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C612" s="3">
+        <v>46261.5</v>
+      </c>
+      <c r="D612" s="6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="613" spans="2:4">
+      <c r="B613" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C613" s="3">
+        <v>46261.722222222219</v>
+      </c>
+      <c r="D613" s="6" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="614" spans="2:4">
+      <c r="B614" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C614" s="3">
+        <v>46262.118055555555</v>
+      </c>
+      <c r="D614" s="6" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="615" spans="2:4">
+      <c r="B615" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C615" s="3">
+        <v>46262.25</v>
+      </c>
+      <c r="D615" s="6" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="616" spans="2:4">
+      <c r="B616" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C616" s="3">
+        <v>46262.427083333336</v>
+      </c>
+      <c r="D616" s="6" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="617" spans="2:4">
+      <c r="B617" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C617" s="3">
+        <v>46262.50277777778</v>
+      </c>
+      <c r="D617" s="6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="618" spans="2:4">
+      <c r="B618" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C618" s="3">
+        <v>46263.194444444445</v>
+      </c>
+      <c r="D618" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="619" spans="2:4">
+      <c r="B619" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C619" s="3">
+        <v>46263.194444444445</v>
+      </c>
+      <c r="D619" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="620" spans="2:4">
+      <c r="B620" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C620" s="3">
+        <v>46263.739583333336</v>
+      </c>
+      <c r="D620" s="6" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="621" spans="2:4">
+      <c r="B621" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C621" s="3">
+        <v>46264.333333333336</v>
+      </c>
+      <c r="D621" s="6" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="622" spans="2:4">
+      <c r="B622" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C622" s="3">
+        <v>46264.708333333336</v>
+      </c>
+      <c r="D622" s="6" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="623" spans="2:4">
+      <c r="B623" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C623" s="3">
+        <v>46265.25</v>
+      </c>
+      <c r="D623" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="624" spans="2:4">
+      <c r="B624" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C624" s="3">
+        <v>46265.25</v>
+      </c>
+      <c r="D624" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="625" spans="2:4">
+      <c r="B625" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C625" s="3">
+        <v>46265.291666666664</v>
+      </c>
+      <c r="D625" s="6" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="626" spans="2:4">
+      <c r="B626" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C626" s="3">
+        <v>46265.569444444445</v>
+      </c>
+      <c r="D626" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="627" spans="2:4">
+      <c r="B627" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C627" s="3">
+        <v>46265.59375</v>
+      </c>
+      <c r="D627" s="6" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="628" spans="2:4">
+      <c r="B628" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C628" s="3">
+        <v>46265.631944444445</v>
+      </c>
+      <c r="D628" s="6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="629" spans="2:4">
+      <c r="B629" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C629" s="3">
+        <v>46265.69027777778</v>
+      </c>
+      <c r="D629" s="6" t="s">
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -8269,7 +9509,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B82532-6694-4B08-9527-A22A4CBED7A9}">
   <dimension ref="B2:K68"/>
-  <sheetFormatPr defaultColWidth="40.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="40.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="38.88671875" bestFit="1" customWidth="1"/>
@@ -8284,44 +9524,44 @@
     <col min="11" max="11" width="109.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="15.6">
       <c r="B2" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="K2" s="12" t="s">
+    </row>
+    <row r="3" spans="2:11" ht="15.6">
+      <c r="B3" s="13" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="3" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>476</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>477</v>
       </c>
       <c r="D3" s="15">
         <v>46095</v>
@@ -8330,30 +9570,30 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="J3" s="18" t="s">
         <v>478</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>479</v>
       </c>
       <c r="K3" s="18" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="15.6">
       <c r="B4" s="13" t="s">
         <v>379</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D4" s="15">
         <v>46113</v>
@@ -8368,24 +9608,24 @@
         <v>0.67708333333333337</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="15.6">
       <c r="B5" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D5" s="15">
         <v>46113</v>
@@ -8401,21 +9641,21 @@
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="14" t="s">
+        <v>481</v>
+      </c>
+      <c r="J5" s="18" t="s">
         <v>482</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>483</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="15.6">
       <c r="B6" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D6" s="15">
         <v>46113</v>
@@ -8430,24 +9670,24 @@
         <v>0.38541666666666669</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="15.6">
       <c r="B7" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D7" s="15">
         <v>46114</v>
@@ -8462,24 +9702,24 @@
         <v>0.3125</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="15.6">
       <c r="B8" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D8" s="15">
         <v>46114</v>
@@ -8494,24 +9734,24 @@
         <v>0.4375</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I8" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="J8" s="18" t="s">
         <v>488</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>489</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="15.6">
       <c r="B9" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D9" s="15">
         <v>46114</v>
@@ -8526,24 +9766,24 @@
         <v>0.5229166666666667</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="15.6">
       <c r="B10" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D10" s="15">
         <v>46114</v>
@@ -8558,24 +9798,24 @@
         <v>0.43819444444444444</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I10" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="J10" s="18" t="s">
         <v>488</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>489</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="15.6">
       <c r="B11" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D11" s="15">
         <v>46114</v>
@@ -8590,24 +9830,24 @@
         <v>0.44027777777777777</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="15.6">
       <c r="B12" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D12" s="15">
         <v>46114</v>
@@ -8625,21 +9865,21 @@
         <v>0.44097222222222221</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="15.6">
       <c r="B13" s="13" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D13" s="15">
         <v>46114</v>
@@ -8654,24 +9894,24 @@
         <v>0.45416666666666666</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="15.6">
       <c r="B14" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D14" s="15">
         <v>46114</v>
@@ -8689,21 +9929,21 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="K14" s="18" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" ht="15.6">
       <c r="B15" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D15" s="15">
         <v>46114</v>
@@ -8718,24 +9958,24 @@
         <v>0.63402777777777775</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K15" s="18" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" ht="15.6">
       <c r="B16" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D16" s="15">
         <v>46115</v>
@@ -8753,21 +9993,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I16" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>499</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>500</v>
       </c>
       <c r="K16" s="18" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" ht="15.6">
       <c r="B17" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D17" s="15">
         <v>46116</v>
@@ -8785,21 +10025,21 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="I17" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="J17" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="K17" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="K17" s="18" t="s">
+    </row>
+    <row r="18" spans="2:11" ht="15.6">
+      <c r="B18" s="13" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="13" t="s">
-        <v>505</v>
-      </c>
       <c r="C18" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D18" s="15">
         <v>46116</v>
@@ -8814,24 +10054,24 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K18" s="18" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="15.6">
       <c r="B19" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D19" s="15">
         <v>46117</v>
@@ -8846,24 +10086,24 @@
         <v>0.46875</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K19" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" ht="15.6">
       <c r="B20" s="20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D20" s="15">
         <v>46117</v>
@@ -8878,24 +10118,24 @@
         <v>0.67847222222222225</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I20" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="J20" s="18" t="s">
         <v>509</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>510</v>
       </c>
       <c r="K20" s="18" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="15.6">
       <c r="B21" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D21" s="15">
         <v>46119</v>
@@ -8913,21 +10153,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" ht="15.6">
       <c r="B22" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D22" s="15">
         <v>46119</v>
@@ -8942,24 +10182,24 @@
         <v>0.49861111111111112</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K22" s="18" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" ht="15.6">
       <c r="B23" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D23" s="15">
         <v>46119</v>
@@ -8974,24 +10214,24 @@
         <v>0.69791666666666663</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I23" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="J23" s="26" t="s">
         <v>514</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>515</v>
       </c>
       <c r="K23" s="18" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" ht="15.6">
       <c r="B24" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D24" s="15">
         <v>46119</v>
@@ -9006,24 +10246,24 @@
         <v>0.71180555555555558</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K24" s="18" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" ht="15.6">
       <c r="B25" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D25" s="15">
         <v>46120</v>
@@ -9038,24 +10278,24 @@
         <v>0.32777777777777778</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K25" s="18" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" ht="15.6">
       <c r="B26" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D26" s="15">
         <v>46120</v>
@@ -9070,24 +10310,24 @@
         <v>0.65486111111111112</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J26" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K26" s="18" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" ht="15.6">
       <c r="B27" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D27" s="15">
         <v>46121</v>
@@ -9105,21 +10345,21 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="I27" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="J27" s="26" t="s">
         <v>521</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>522</v>
       </c>
       <c r="K27" s="18" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" ht="15.6">
       <c r="B28" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D28" s="15">
         <v>46121</v>
@@ -9134,24 +10374,24 @@
         <v>0.39097222222222222</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I28" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="J28" s="26" t="s">
         <v>523</v>
-      </c>
-      <c r="J28" s="26" t="s">
-        <v>524</v>
       </c>
       <c r="K28" s="18" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" ht="15.6">
       <c r="B29" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D29" s="15">
         <v>46121</v>
@@ -9166,24 +10406,24 @@
         <v>0.43541666666666667</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J29" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="K29" s="18" t="s">
         <v>524</v>
       </c>
-      <c r="K29" s="18" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:11" ht="15.6">
       <c r="B30" s="14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D30" s="15">
         <v>46122</v>
@@ -9198,24 +10438,24 @@
         <v>0.3263888888888889</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J30" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="K30" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="K30" s="18" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:11" ht="15.6">
       <c r="B31" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D31" s="15">
         <v>46122</v>
@@ -9230,24 +10470,24 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K31" s="18" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" ht="15.6">
       <c r="B32" s="14" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D32" s="15">
         <v>46123</v>
@@ -9265,21 +10505,21 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="I32" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="J32" s="26" t="s">
         <v>529</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>530</v>
       </c>
       <c r="K32" s="18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" ht="15.6">
       <c r="B33" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D33" s="15">
         <v>46123</v>
@@ -9294,24 +10534,24 @@
         <v>0.3576388888888889</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K33" s="18" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="34" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" ht="15.6">
       <c r="B34" s="14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D34" s="15">
         <v>46124</v>
@@ -9329,21 +10569,21 @@
         <v>0.30208333333333331</v>
       </c>
       <c r="I34" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="J34" s="26" t="s">
         <v>533</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>534</v>
       </c>
       <c r="K34" s="18" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="35" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" ht="15.6">
       <c r="B35" s="14" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D35" s="15">
         <v>46124</v>
@@ -9358,24 +10598,24 @@
         <v>0.29305555555555557</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K35" s="18" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" ht="15.6">
       <c r="B36" s="14" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D36" s="15">
         <v>46125</v>
@@ -9393,21 +10633,21 @@
         <v>0.38333333333333336</v>
       </c>
       <c r="I36" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="J36" s="26" t="s">
         <v>538</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>539</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" ht="15.6">
       <c r="B37" s="14" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D37" s="15">
         <v>46126</v>
@@ -9422,24 +10662,24 @@
         <v>0.34444444444444444</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K37" s="18" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" ht="15.6">
       <c r="B38" s="21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D38" s="15">
         <v>46126</v>
@@ -9454,24 +10694,24 @@
         <v>0.34722222222222221</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K38" s="18" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" ht="15.6">
       <c r="B39" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D39" s="15">
         <v>46129</v>
@@ -9489,21 +10729,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K39" s="24" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" ht="15.6">
       <c r="B40" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D40" s="15">
         <v>46130</v>
@@ -9512,30 +10752,30 @@
         <v>0.56944444444444442</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H40" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J40" s="26" t="s">
+        <v>543</v>
+      </c>
+      <c r="K40" s="18" t="s">
         <v>544</v>
       </c>
-      <c r="K40" s="18" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="2:11" ht="15.6">
       <c r="B41" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D41" s="15">
         <v>46130</v>
@@ -9553,21 +10793,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K41" s="18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" ht="15.6">
       <c r="B42" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D42" s="15">
         <v>46131</v>
@@ -9585,21 +10825,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I42" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="J42" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="J42" s="26" t="s">
+      <c r="K42" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="K42" s="18" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:11" ht="15.6">
       <c r="B43" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D43" s="15">
         <v>46131</v>
@@ -9617,21 +10857,21 @@
         <v>0.375</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K43" s="18" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" ht="15.6">
       <c r="B44" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D44" s="15">
         <v>46131</v>
@@ -9649,21 +10889,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I44" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="J44" s="18" t="s">
         <v>550</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>551</v>
       </c>
       <c r="K44" s="18" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" ht="15.6">
       <c r="B45" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D45" s="15">
         <v>46131</v>
@@ -9681,21 +10921,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K45" s="18" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="46" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" ht="15.6">
       <c r="B46" s="14" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D46" s="15">
         <v>46132</v>
@@ -9710,24 +10950,24 @@
         <v>0.25624999999999998</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I46" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="J46" s="26" t="s">
         <v>554</v>
-      </c>
-      <c r="J46" s="26" t="s">
-        <v>555</v>
       </c>
       <c r="K46" s="18" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="47" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" ht="15.6">
       <c r="B47" s="14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D47" s="15">
         <v>46132</v>
@@ -9742,24 +10982,24 @@
         <v>0.26111111111111113</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K47" s="18" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="48" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" ht="15.6">
       <c r="B48" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D48" s="15">
         <v>46134</v>
@@ -9774,24 +11014,24 @@
         <v>0.47083333333333333</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K48" s="18" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="49" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11" ht="15.6">
       <c r="B49" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D49" s="15">
         <v>46134</v>
@@ -9806,24 +11046,24 @@
         <v>0.49930555555555556</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K49" s="18" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="50" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11" ht="15.6">
       <c r="B50" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D50" s="15">
         <v>46134</v>
@@ -9838,24 +11078,24 @@
         <v>0.62708333333333333</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K50" s="18" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="51" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11" ht="15.6">
       <c r="B51" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D51" s="15">
         <v>46135</v>
@@ -9873,21 +11113,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K51" s="18" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="52" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11" ht="15.6">
       <c r="B52" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D52" s="15">
         <v>46135</v>
@@ -9905,21 +11145,21 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K52" s="18" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="53" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11" ht="15.6">
       <c r="B53" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D53" s="15">
         <v>46136</v>
@@ -9928,30 +11168,30 @@
         <v>0.25</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J53" s="26" t="s">
+        <v>558</v>
+      </c>
+      <c r="K53" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="K53" s="18" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="2:11" ht="15.6">
       <c r="B54" s="14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D54" s="15">
         <v>46136</v>
@@ -9960,30 +11200,30 @@
         <v>0.25</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G54" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J54" s="26" t="s">
+        <v>560</v>
+      </c>
+      <c r="K54" s="18" t="s">
         <v>561</v>
       </c>
-      <c r="K54" s="18" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="2:11" ht="15.6">
       <c r="B55" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D55" s="15">
         <v>46136</v>
@@ -10000,18 +11240,18 @@
       <c r="H55" s="16"/>
       <c r="I55" s="14"/>
       <c r="J55" s="26" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K55" s="18" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11" ht="15.6">
       <c r="B56" s="14" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D56" s="15">
         <v>46136</v>
@@ -10026,24 +11266,24 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K56" s="18" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="57" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11" ht="15.6">
       <c r="B57" s="14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D57" s="15">
         <v>46137</v>
@@ -10052,30 +11292,30 @@
         <v>0.25</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G57" s="25" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J57" s="26" t="s">
+        <v>563</v>
+      </c>
+      <c r="K57" s="18" t="s">
         <v>564</v>
       </c>
-      <c r="K57" s="18" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="2:11" ht="15.6">
       <c r="B58" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D58" s="15">
         <v>46137</v>
@@ -10090,24 +11330,24 @@
         <v>0.51458333333333328</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J58" s="26" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K58" s="18" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="59" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:11" ht="15.6">
       <c r="B59" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D59" s="15">
         <v>46137</v>
@@ -10125,21 +11365,21 @@
         <v>0.52083333333333337</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K59" s="18" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:11" ht="15.6">
       <c r="B60" s="14" t="s">
         <v>379</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D60" s="15">
         <v>46138</v>
@@ -10154,24 +11394,24 @@
         <v>0.3125</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K60" s="18" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="61" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:11" ht="15.6">
       <c r="B61" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D61" s="15">
         <v>46139</v>
@@ -10186,24 +11426,24 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J61" s="26" t="s">
+        <v>568</v>
+      </c>
+      <c r="K61" s="18" t="s">
         <v>569</v>
       </c>
-      <c r="K61" s="18" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="2:11" ht="15.6">
       <c r="B62" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D62" s="15">
         <v>46139</v>
@@ -10221,21 +11461,21 @@
         <v>0.65625</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J62" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K62" s="18" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="63" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:11" ht="15.6">
       <c r="B63" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D63" s="15">
         <v>46139</v>
@@ -10250,24 +11490,24 @@
         <v>0.30555555555555558</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K63" s="18" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:11" ht="15.6">
       <c r="B64" s="14" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D64" s="15">
         <v>46140</v>
@@ -10282,24 +11522,24 @@
         <v>0.75555555555555554</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K64" s="18" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="65" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11" ht="15.6">
       <c r="B65" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D65" s="15">
         <v>46141</v>
@@ -10317,21 +11557,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K65" s="18" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="66" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11" ht="15.6">
       <c r="B66" s="14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D66" s="15">
         <v>46141</v>
@@ -10349,21 +11589,21 @@
         <v>0.29166666666666669</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K66" s="18" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="67" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11" ht="15.6">
       <c r="B67" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D67" s="15">
         <v>46141</v>
@@ -10378,24 +11618,24 @@
         <v>0.61111111111111116</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K67" s="18" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11" ht="15.6">
       <c r="B68" s="14" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D68" s="15">
         <v>46141</v>
@@ -10411,13 +11651,1587 @@
       </c>
       <c r="H68" s="16"/>
       <c r="I68" s="14" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K68" s="18" t="s">
         <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F4E357-577A-48CD-A40C-9C0C2C5D09D3}">
+  <dimension ref="A1:F78"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="102.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15">
+      <c r="A1" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C1" s="36">
+        <v>46237.208333333336</v>
+      </c>
+      <c r="D1" s="36">
+        <v>46237.302083333336</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15">
+      <c r="A2" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C2" s="36">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="D2" s="36">
+        <v>46237.395833333336</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15">
+      <c r="A3" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C3" s="36">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="D3" s="36">
+        <v>46237.597222222219</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
+      <c r="A4" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C4" s="36">
+        <v>46237.40625</v>
+      </c>
+      <c r="D4" s="36">
+        <v>46237.416666666664</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
+      <c r="A5" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C5" s="36">
+        <v>46237.434027777781</v>
+      </c>
+      <c r="D5" s="36">
+        <v>46237.458333333336</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15">
+      <c r="A6" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C6" s="36">
+        <v>46237.749305555553</v>
+      </c>
+      <c r="D6" s="36">
+        <v>46237.756944444445</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" s="30" t="s">
+        <v>578</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C7" s="36">
+        <v>46238.28402777778</v>
+      </c>
+      <c r="D7" s="36">
+        <v>46238.287499999999</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="A8" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C8" s="36">
+        <v>46238.325694444444</v>
+      </c>
+      <c r="D8" s="36">
+        <v>46238.345833333333</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C9" s="36">
+        <v>46238.571527777778</v>
+      </c>
+      <c r="D9" s="36">
+        <v>46238.573611111111</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C10" s="36">
+        <v>46239.586805555555</v>
+      </c>
+      <c r="D10" s="36">
+        <v>46241.576388888891</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15">
+      <c r="A11" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C11" s="38">
+        <v>46240.491666666669</v>
+      </c>
+      <c r="D11" s="38">
+        <v>46240.736805555556</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15">
+      <c r="A12" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C12" s="38">
+        <v>46240.517361111109</v>
+      </c>
+      <c r="D12" s="38">
+        <v>46241.316666666666</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15">
+      <c r="A13" s="31" t="s">
+        <v>580</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C13" s="38">
+        <v>46241.340277777781</v>
+      </c>
+      <c r="D13" s="38">
+        <v>46241.361111111109</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15">
+      <c r="A14" s="31" t="s">
+        <v>577</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C14" s="38">
+        <v>46241.416666666664</v>
+      </c>
+      <c r="D14" s="38">
+        <v>46241.419444444444</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15">
+      <c r="A15" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C15" s="38">
+        <v>46241.51458333333</v>
+      </c>
+      <c r="D15" s="38">
+        <v>46241.519444444442</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15">
+      <c r="A16" s="31" t="s">
+        <v>580</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C16" s="38">
+        <v>46241.670138888891</v>
+      </c>
+      <c r="D16" s="38">
+        <v>46241.677777777775</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15">
+      <c r="A17" s="31" t="s">
+        <v>582</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C17" s="38">
+        <v>46242.579861111109</v>
+      </c>
+      <c r="D17" s="38">
+        <v>46242.631944444445</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15">
+      <c r="A18" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C18" s="38">
+        <v>46242.729166666664</v>
+      </c>
+      <c r="D18" s="38">
+        <v>46243.333333333336</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15">
+      <c r="A19" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C19" s="38">
+        <v>46242.759027777778</v>
+      </c>
+      <c r="D19" s="38">
+        <v>46243.291666666664</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15">
+      <c r="A20" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C20" s="38">
+        <v>46243.291666666664</v>
+      </c>
+      <c r="D20" s="38">
+        <v>46243.590277777781</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15">
+      <c r="A21" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>637</v>
+      </c>
+      <c r="C21" s="38">
+        <v>46243.614583333336</v>
+      </c>
+      <c r="D21" s="38">
+        <v>46243.623611111114</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15">
+      <c r="A22" s="31" t="s">
+        <v>580</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C22" s="38">
+        <v>46243.642361111109</v>
+      </c>
+      <c r="D22" s="38">
+        <v>46243.651388888888</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15">
+      <c r="A23" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C23" s="38">
+        <v>46243.942361111112</v>
+      </c>
+      <c r="D23" s="38">
+        <v>46244.3125</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15">
+      <c r="A24" s="31" t="s">
+        <v>584</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C24" s="38">
+        <v>46244.413194444445</v>
+      </c>
+      <c r="D24" s="38">
+        <v>46244.444444444445</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15">
+      <c r="A25" s="31" t="s">
+        <v>576</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C25" s="38">
+        <v>46244.951388888891</v>
+      </c>
+      <c r="D25" s="38">
+        <v>46244.326388888891</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F25" s="34" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" s="31" t="s">
+        <v>576</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C26" s="38">
+        <v>46245.40625</v>
+      </c>
+      <c r="D26" s="38">
+        <v>46245.410416666666</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15">
+      <c r="A27" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C27" s="38">
+        <v>46245.479166666664</v>
+      </c>
+      <c r="D27" s="38">
+        <v>46245.482638888891</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C28" s="38">
+        <v>46245.522222222222</v>
+      </c>
+      <c r="D28" s="38">
+        <v>46245.524305555555</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F28" s="34" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15">
+      <c r="A29" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C29" s="38">
+        <v>46247.347222222219</v>
+      </c>
+      <c r="D29" s="38">
+        <v>46247.381944444445</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F29" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C30" s="38">
+        <v>46247.440972222219</v>
+      </c>
+      <c r="D30" s="38">
+        <v>46247.447916666664</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15">
+      <c r="A31" s="31" t="s">
+        <v>585</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C31" s="38">
+        <v>46248.30972222222</v>
+      </c>
+      <c r="D31" s="38">
+        <v>46248.311111111114</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" s="31" t="s">
+        <v>580</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C32" s="38">
+        <v>46249.361111111109</v>
+      </c>
+      <c r="D32" s="38">
+        <v>46254.375</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C33" s="38">
+        <v>46249.607638888891</v>
+      </c>
+      <c r="D33" s="38">
+        <v>46249.612500000003</v>
+      </c>
+      <c r="E33" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F33" s="34" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" s="31" t="s">
+        <v>577</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C34" s="38">
+        <v>46250.541666666664</v>
+      </c>
+      <c r="D34" s="38">
+        <v>46250.601388888892</v>
+      </c>
+      <c r="E34" s="39">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="F34" s="34" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15">
+      <c r="A35" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C35" s="38">
+        <v>46252.458333333336</v>
+      </c>
+      <c r="D35" s="38">
+        <v>46252.740972222222</v>
+      </c>
+      <c r="E35" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F35" s="34" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="A36" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C36" s="38">
+        <v>46252.460416666669</v>
+      </c>
+      <c r="D36" s="38">
+        <v>46252.630555555559</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F36" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15">
+      <c r="A37" s="31" t="s">
+        <v>582</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C37" s="38">
+        <v>46252.552083333336</v>
+      </c>
+      <c r="D37" s="38">
+        <v>46252.6875</v>
+      </c>
+      <c r="E37" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15">
+      <c r="A38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C38" s="38">
+        <v>46253.229166666664</v>
+      </c>
+      <c r="D38" s="38">
+        <v>46253.361111111109</v>
+      </c>
+      <c r="E38" s="39">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="F38" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15">
+      <c r="A39" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>636</v>
+      </c>
+      <c r="C39" s="40">
+        <v>46253.447916666664</v>
+      </c>
+      <c r="D39" s="40">
+        <v>46255.381944444445</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>477</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15">
+      <c r="A40" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C40" s="38">
+        <v>46253.583333333336</v>
+      </c>
+      <c r="D40" s="38">
+        <v>46254.479166666664</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15">
+      <c r="A41" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C41" s="38">
+        <v>46254.427083333336</v>
+      </c>
+      <c r="D41" s="38">
+        <v>46254.569444444445</v>
+      </c>
+      <c r="E41" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F41" s="34" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15">
+      <c r="A42" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C42" s="38">
+        <v>46254.576388888891</v>
+      </c>
+      <c r="D42" s="38">
+        <v>46254.893750000003</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15">
+      <c r="A43" s="31" t="s">
+        <v>588</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C43" s="38">
+        <v>46254.708333333336</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C44" s="38">
+        <v>46255.3125</v>
+      </c>
+      <c r="D44" s="38">
+        <v>46255.534722222219</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15">
+      <c r="A45" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C45" s="38">
+        <v>46255.548611111109</v>
+      </c>
+      <c r="D45" s="38">
+        <v>46255.631944444445</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F45" s="34" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15">
+      <c r="A46" s="31" t="s">
+        <v>576</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C46" s="38">
+        <v>46256.088194444441</v>
+      </c>
+      <c r="D46" s="38">
+        <v>46256.306944444441</v>
+      </c>
+      <c r="E46" s="39"/>
+      <c r="F46" s="34" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15">
+      <c r="A47" s="31" t="s">
+        <v>589</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C47" s="38">
+        <v>46256.394444444442</v>
+      </c>
+      <c r="D47" s="38">
+        <v>46259.32916666667</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F47" s="34" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15">
+      <c r="A48" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C48" s="38">
+        <v>46257.40347222222</v>
+      </c>
+      <c r="D48" s="38">
+        <v>46257.408333333333</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15">
+      <c r="A49" s="31" t="s">
+        <v>590</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C49" s="38">
+        <v>46257.534722222219</v>
+      </c>
+      <c r="D49" s="38">
+        <v>46257.59375</v>
+      </c>
+      <c r="E49" s="39">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15">
+      <c r="A50" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>637</v>
+      </c>
+      <c r="C50" s="38">
+        <v>46257.638888888891</v>
+      </c>
+      <c r="D50" s="38">
+        <v>46257.652777777781</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F50" s="34" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15">
+      <c r="A51" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C51" s="38">
+        <v>46257.913888888892</v>
+      </c>
+      <c r="D51" s="38">
+        <v>46258.333333333336</v>
+      </c>
+      <c r="E51" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F51" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15">
+      <c r="A52" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C52" s="38">
+        <v>46258.494664351849</v>
+      </c>
+      <c r="D52" s="38">
+        <v>46258.508888888886</v>
+      </c>
+      <c r="E52" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F52" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15">
+      <c r="A53" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C53" s="38">
+        <v>46259.371527777781</v>
+      </c>
+      <c r="D53" s="38">
+        <v>46259.381249999999</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" s="31" t="s">
+        <v>586</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C54" s="38">
+        <v>46259.390972222223</v>
+      </c>
+      <c r="D54" s="38">
+        <v>46259.649305555555</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C55" s="38">
+        <v>46259.545138888891</v>
+      </c>
+      <c r="D55" s="38">
+        <v>46259.581250000003</v>
+      </c>
+      <c r="E55" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F55" s="34" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15">
+      <c r="A56" s="31" t="s">
+        <v>579</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C56" s="38">
+        <v>46259.5625</v>
+      </c>
+      <c r="D56" s="38">
+        <v>46259.638888888891</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15">
+      <c r="A57" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C57" s="38">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="D57" s="38">
+        <v>46261.095833333333</v>
+      </c>
+      <c r="E57" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15">
+      <c r="A58" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C58" s="38">
+        <v>46261.262499999997</v>
+      </c>
+      <c r="D58" s="38">
+        <v>46261.277777777781</v>
+      </c>
+      <c r="E58" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15">
+      <c r="A59" s="31" t="s">
+        <v>589</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C59" s="38">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="D59" s="38">
+        <v>46261.340277777781</v>
+      </c>
+      <c r="E59" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F59" s="34" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15">
+      <c r="A60" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C60" s="38">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="D60" s="38">
+        <v>46261.479166666664</v>
+      </c>
+      <c r="E60" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15">
+      <c r="A61" s="31" t="s">
+        <v>576</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C61" s="38">
+        <v>46261.340277777781</v>
+      </c>
+      <c r="D61" s="38">
+        <v>46261.379861111112</v>
+      </c>
+      <c r="E61" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15">
+      <c r="A62" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C62" s="38">
+        <v>46261.444444444445</v>
+      </c>
+      <c r="D62" s="38">
+        <v>46261.493055555555</v>
+      </c>
+      <c r="E62" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15">
+      <c r="A63" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C63" s="36">
+        <v>46261.5</v>
+      </c>
+      <c r="D63" s="36">
+        <v>46262.25</v>
+      </c>
+      <c r="E63" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F63" s="34" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15">
+      <c r="A64" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="C64" s="38">
+        <v>46261.722222222219</v>
+      </c>
+      <c r="D64" s="38">
+        <v>46262.170138888891</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F64" s="34" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15">
+      <c r="A65" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C65" s="36">
+        <v>46262.118055555555</v>
+      </c>
+      <c r="D65" s="36">
+        <v>46262.357638888891</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F65" s="34" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15">
+      <c r="A66" s="31" t="s">
+        <v>583</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>638</v>
+      </c>
+      <c r="C66" s="36">
+        <v>46262.25</v>
+      </c>
+      <c r="D66" s="36">
+        <v>46262.423611111109</v>
+      </c>
+      <c r="E66" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F66" s="34" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15">
+      <c r="A67" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C67" s="36">
+        <v>46262.427083333336</v>
+      </c>
+      <c r="D67" s="36">
+        <v>46262.534722222219</v>
+      </c>
+      <c r="E67" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15">
+      <c r="A68" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C68" s="36">
+        <v>46262.50277777778</v>
+      </c>
+      <c r="D68" s="36">
+        <v>46262.550694444442</v>
+      </c>
+      <c r="E68" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15">
+      <c r="A69" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C69" s="36">
+        <v>46263.194444444445</v>
+      </c>
+      <c r="D69" s="36">
+        <v>46263.3125</v>
+      </c>
+      <c r="E69" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15">
+      <c r="A70" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C70" s="36">
+        <v>46263.739583333336</v>
+      </c>
+      <c r="D70" s="36">
+        <v>46266.666666666664</v>
+      </c>
+      <c r="E70" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F70" s="34" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15">
+      <c r="A71" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>638</v>
+      </c>
+      <c r="C71" s="36">
+        <v>46264.333333333336</v>
+      </c>
+      <c r="D71" s="36">
+        <v>46264.5</v>
+      </c>
+      <c r="E71" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F71" s="34" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15">
+      <c r="A72" s="30" t="s">
+        <v>591</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C72" s="36">
+        <v>46264.708333333336</v>
+      </c>
+      <c r="D72" s="36">
+        <v>46264.315972222219</v>
+      </c>
+      <c r="E72" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F72" s="34" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15">
+      <c r="A73" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C73" s="36">
+        <v>46265.25</v>
+      </c>
+      <c r="D73" s="36">
+        <v>46265.316666666666</v>
+      </c>
+      <c r="E73" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15">
+      <c r="A74" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>638</v>
+      </c>
+      <c r="C74" s="36">
+        <v>46265.291666666664</v>
+      </c>
+      <c r="D74" s="36">
+        <v>46265.479166666664</v>
+      </c>
+      <c r="E74" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15">
+      <c r="A75" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C75" s="36">
+        <v>46265.569444444445</v>
+      </c>
+      <c r="D75" s="36">
+        <v>46265.701388888891</v>
+      </c>
+      <c r="E75" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15">
+      <c r="A76" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C76" s="36">
+        <v>46265.59375</v>
+      </c>
+      <c r="D76" s="36">
+        <v>46265.618055555555</v>
+      </c>
+      <c r="E76" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F76" s="34" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15">
+      <c r="A77" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C77" s="36">
+        <v>46265.631944444445</v>
+      </c>
+      <c r="D77" s="36">
+        <v>46265.692361111112</v>
+      </c>
+      <c r="E77" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15">
+      <c r="A78" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>636</v>
+      </c>
+      <c r="C78" s="36">
+        <v>46265.69027777778</v>
+      </c>
+      <c r="D78" s="36">
+        <v>46265.693055555559</v>
+      </c>
+      <c r="E78" s="39" t="s">
+        <v>477</v>
+      </c>
+      <c r="F78" s="34" t="s">
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -10442,6 +13256,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100129872B20EB72F43A65F017F96B1C226" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8918ff54d439e714c6ec094a8552ca51">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae836115-58a4-4701-a509-51b7f29d6ef2" xmlns:ns3="f2c58eb1-9d7f-4123-980d-e0326d949ea4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dac983c0446f866ea106b147c21f2a9" ns2:_="" ns3:_="">
     <xsd:import namespace="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
@@ -10701,27 +13524,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D474CDF3-F77E-4C91-BAE3-2259CB3B5596}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="f2c58eb1-9d7f-4123-980d-e0326d949ea4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{479B8213-A263-4381-AC21-345AF9A36A7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10738,12 +13566,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/thopen/data/Polaris/Comentários Polaris.xlsx
+++ b/thopen/data/Polaris/Comentários Polaris.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gridcobr-my.sharepoint.com/personal/levi_maia_gridco_com_br/Documents/Área de Trabalho/temp/Projeto API PV/thopen/data/Polaris/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1623" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FA92028-3E41-46C8-A56A-E78CA0FF2D9A}"/>
+  <xr:revisionPtr revIDLastSave="1764" documentId="8_{ED9FA5F1-FA4F-4FDB-85FE-BA726058332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{322760F4-A9C0-488A-8298-E6BA6FD25E43}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C1E55A4-6A58-4802-A746-28D27D2A414B}"/>
   </bookViews>
   <sheets>
     <sheet name="Comentários" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
-    <sheet name="Planilha2" sheetId="3" r:id="rId3"/>
+    <sheet name="Planilha3" sheetId="4" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="2" r:id="rId3"/>
+    <sheet name="Planilha2" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="717">
   <si>
     <t>UFV 1</t>
   </si>
@@ -1960,6 +1961,240 @@
   </si>
   <si>
     <t>Inversor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 59 - 03/08/2026 05:00 ás 03/08/2026 07:15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 59N E 67 - 03/08/2026 06:20 ás 03/08/2026 09:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 03/08/2026 06:20 ás 03/08/2026 14:20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 80 E 81 - 03/08/2026 09:45 ás 03/08/2026 10:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 59 - 03/08/2026 10:25 ás 03/08/2026 11:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 59N (Religamento Remoto) - 03/08/2026 17:59 ás 03/08/2026 18:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 81 (Religamento Remoto) - 04/08/2026 06:49 ás 04/08/2026 06:54 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 04/08/2026 07:49 ás 04/08/2026 08:18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 81 (Religamento Remoto) - 04/08/2026 13:43 ás 04/08/2026 13:46 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Devido Chave Faca Da Concessionária Atuado - 05/08/2026 14:05 ás 07/08/2026 13:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Por Parte Da Concessionária - 06/08/2026 11:48 ás 06/08/2026 17:41 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Devido Manutenção Programada Na Rede, Por Parte Da Concessionária, Trip 27 E 59N - 06/08/2026 12:25 ás 07/08/2026 07:36 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 (Religamento Remoto) - 07/08/2026 08:10 ás 07/08/2026 08:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 59N (Religamento Remoto) - 07/08/2026 10:00 ás 07/08/2026 10:04 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 32 (Religamento Remoto) - 07/08/2026 12:21 ás 07/08/2026 12:28 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 (Religamento Remoto) - 07/08/2026 16:05 ás 07/08/2026 16:16 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Sem Proteção/Trip Ativo - 08/08/2026 13:55 ás 08/08/2026 15:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 08/08/2026 17:30 ás 09/08/2026 08:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Apenas Falha De Comunicação Com O Supervisório - 08/08/2026 18:13 ás 09/08/2026 07:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Inversor Nº 5 Em Falha/Desligado - 09/08/2026 07:00 ás 09/08/2026 14:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabine - Usina Desligada, Relé Trip 47 (Religamento Remoto) - 09/08/2026 14:45 ás 09/08/2026 14:58 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 09/08/2026 15:25 ás 09/08/2026 15:38 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 09/08/2026 22:37 ás 10/08/2026 07:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 32, 50, 51 E 67 - 10/08/2026 09:55 ás 10/08/2026 10:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 59 - 10/08/2026 22:50 ás 11/08/2026 07:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 59 - 11/08/2026 09:45 ás 11/08/2026 09:51 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 11/08/2026 11:30 ás 11/08/2026 11:35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé 32 (Religamento Remoto) - 11/08/2026 12:32 ás 11/08/2026 12:35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 13/08/2026 08:20 ás 13/08/2026 09:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 (Religamento Remoto) - 13/08/2026 10:35 ás 13/08/2026 10:45 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 81 (Religamento Remoto) - 14/08/2026 07:26 ás 14/08/2026 07:28 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 1 Em Falha/Desligado - 15/08/2026 08:40 ás 20/08/2026 09:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 32 (Religamento Remoto) - 15/08/2026 14:35 ás 15/08/2026 14:42 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 59N - 16/08/2026 13:00 ás 16/08/2026 14:26 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Falha De Comunicação Devido Fibra Rompida Na Região - 18/08/2026 11:00 ás 18/08/2026 17:47 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 18/08/2026 11:03 ás 18/08/2026 15:08 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 50 E 51 - 18/08/2026 13:15 ás 18/08/2026 16:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 19/08/2026 05:30 ás 19/08/2026 08:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Mas Em Falha De Comunicação, Devido Falta De Internet - 19/08/2026 10:45 ás 21/08/2026 09:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 2 Em Falha/Desligado - 19/08/2026 14:00 ás 20/08/2026 11:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27 - 20/08/2026 10:15 ás 20/08/2026 13:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada - 20/08/2026 13:50 ás 20/08/2026 21:27 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Falha De Comunicação Com O Supervisório - 20/08/2026 17:00 ás 10/09/2026 10:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Mas Em Falha De Comunicação, Devido Falta De Internet - 21/08/2026 07:30 ás 21/08/2026 12:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Mas Em Falha De Comunicação, Devido Falta De Internet - 21/08/2026 13:10 ás 21/08/2026 15:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 59 - 22/08/2026 02:07 ás 22/08/2026 07:22 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Curto No Pde - 22/08/2026 09:28 ás 25/08/2026 07:54 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 (Religado Remotamente) - 23/08/2026 09:41 ás 23/08/2026 09:48 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 67 - 23/08/2026 12:50 ás 23/08/2026 14:15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabine - Usina Desligada, Relé Trip 47 (Religado Remotamente) - 23/08/2026 15:20 ás 23/08/2026 15:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 23/08/2026 21:56 ás 24/08/2026 08:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 24/08/2026 11:52 ás 24/08/2026 12:12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 25/08/2026 08:55 ás 25/08/2026 09:09 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27 - 25/08/2026 09:23 ás 25/08/2026 15:35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 50, 51 E 67 - 25/08/2026 13:05 ás 25/08/2026 13:57 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 25/08/2026 13:30 ás 25/08/2026 15:20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Manutenção Programada - Mpa - 26/08/2026 17:45 ás 27/08/2026 02:18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 27/08/2026 06:18 ás 27/08/2026 06:40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 6 Em Falha/Desligado - 27/08/2026 07:00 ás 27/08/2026 08:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 2 Ligado, Mas Em Falha De Comunicação - 27/08/2026 07:00 ás 27/08/2026 11:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 47 E 59 - 27/08/2026 08:10 ás 27/08/2026 09:07 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Campo) 50 E 51 (Supervisório) - 27/08/2026 10:40 ás 27/08/2026 11:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 8 Ligado, Mas Em Falha De Comunicação - 27/08/2026 12:00 ás 28/08/2026 06:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Falha De Comunicação Devido Fibra Rompida Na Região - 28/08/2026 02:50 ás 28/08/2026 08:35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 1 E 2 Ligado, Mas Em Falha De Comunicação - 28/08/2026 06:00 ás 28/08/2026 10:10 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada - 28/08/2026 10:15 ás 28/08/2026 12:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 50 E 51 - 28/08/2026 12:04 ás 28/08/2026 13:13 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 29/08/2026 04:40 ás 29/08/2026 07:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Ligada, Mas Em Falha De Comunicação, Devido Falta De Internet - 29/08/2026 17:45 ás 01/09/2026 16:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversor Nº 4, 5, 6 E 14 Ligado, Mas Em Falha De Comunicação - 30/08/2026 08:00 ás 30/08/2026 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip - 30/08/2026 17:00 ás 31/08/2026 07:35 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc - 31/08/2026 06:00 ás 31/08/2026 07:36 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 27Abc E 47 - 31/08/2026 13:40 ás 31/08/2026 16:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 32Abc (Religamento Remoto) - 31/08/2026 14:15 ás 31/08/2026 14:50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Trip 81 - 31/08/2026 15:10 ás 31/08/2026 16:37 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usina - Usina Desligada, Relé Sem Trip (Religamento Remoto) - 31/08/2026 16:34 ás 31/08/2026 16:38 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inversor - Inversores Nº 4, 5, 6 E 14 Em Falha De Comunicação Com O Supervisório - 31/08/2026 07:00 ás 31/08/2026 11:30 </t>
+  </si>
+  <si>
+    <t>Desligamento usina - Manutenção programada (MPA) - 27/08 às 17:20h ao 28/08 às 04:05h (Araçoiaba da Serra IB)</t>
   </si>
 </sst>
 </file>
@@ -2097,7 +2332,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2183,9 +2418,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2221,6 +2453,12 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8426,7 +8664,7 @@
       <c r="C532" s="3">
         <v>46199</v>
       </c>
-      <c r="D532" s="29" t="s">
+      <c r="D532" s="4" t="s">
         <v>461</v>
       </c>
     </row>
@@ -8437,7 +8675,7 @@
       <c r="C533" s="3">
         <v>46199</v>
       </c>
-      <c r="D533" s="29" t="s">
+      <c r="D533" s="4" t="s">
         <v>462</v>
       </c>
     </row>
@@ -8448,7 +8686,7 @@
       <c r="C534" s="3">
         <v>46199</v>
       </c>
-      <c r="D534" s="29" t="s">
+      <c r="D534" s="4" t="s">
         <v>462</v>
       </c>
     </row>
@@ -8459,7 +8697,7 @@
       <c r="C535" s="3">
         <v>46200</v>
       </c>
-      <c r="D535" s="29" t="s">
+      <c r="D535" s="4" t="s">
         <v>463</v>
       </c>
     </row>
@@ -8470,7 +8708,7 @@
       <c r="C536" s="3">
         <v>46200</v>
       </c>
-      <c r="D536" s="29" t="s">
+      <c r="D536" s="4" t="s">
         <v>463</v>
       </c>
     </row>
@@ -8481,7 +8719,7 @@
       <c r="C537" s="3">
         <v>46200</v>
       </c>
-      <c r="D537" s="29" t="s">
+      <c r="D537" s="4" t="s">
         <v>464</v>
       </c>
     </row>
@@ -8492,7 +8730,7 @@
       <c r="C538" s="3">
         <v>46200</v>
       </c>
-      <c r="D538" s="29" t="s">
+      <c r="D538" s="4" t="s">
         <v>464</v>
       </c>
     </row>
@@ -8503,8 +8741,8 @@
       <c r="C539" s="3">
         <v>46237.208333333336</v>
       </c>
-      <c r="D539" s="6" t="s">
-        <v>592</v>
+      <c r="D539" s="4" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="540" spans="2:4">
@@ -8514,19 +8752,19 @@
       <c r="C540" s="3">
         <v>46237.263888888891</v>
       </c>
-      <c r="D540" s="6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="541" spans="2:4">
+      <c r="D540" s="4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="541" spans="2:4" ht="14.4" customHeight="1">
       <c r="B541" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C541" s="3">
         <v>46237.263888888891</v>
       </c>
-      <c r="D541" s="6" t="s">
-        <v>594</v>
+      <c r="D541" s="4" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="542" spans="2:4">
@@ -8536,8 +8774,8 @@
       <c r="C542" s="3">
         <v>46237.40625</v>
       </c>
-      <c r="D542" s="6" t="s">
-        <v>595</v>
+      <c r="D542" s="4" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="543" spans="2:4">
@@ -8547,8 +8785,8 @@
       <c r="C543" s="3">
         <v>46237.434027777781</v>
       </c>
-      <c r="D543" s="6" t="s">
-        <v>596</v>
+      <c r="D543" s="4" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="544" spans="2:4">
@@ -8558,8 +8796,8 @@
       <c r="C544" s="3">
         <v>46237.749305555553</v>
       </c>
-      <c r="D544" s="6" t="s">
-        <v>597</v>
+      <c r="D544" s="4" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="545" spans="2:4">
@@ -8569,8 +8807,8 @@
       <c r="C545" s="3">
         <v>46238.28402777778</v>
       </c>
-      <c r="D545" s="6" t="s">
-        <v>598</v>
+      <c r="D545" s="4" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="546" spans="2:4">
@@ -8580,8 +8818,8 @@
       <c r="C546" s="3">
         <v>46238.28402777778</v>
       </c>
-      <c r="D546" s="6" t="s">
-        <v>598</v>
+      <c r="D546" s="4" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="547" spans="2:4">
@@ -8591,8 +8829,8 @@
       <c r="C547" s="3">
         <v>46238.325694444444</v>
       </c>
-      <c r="D547" s="6" t="s">
-        <v>594</v>
+      <c r="D547" s="4" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="548" spans="2:4">
@@ -8602,8 +8840,8 @@
       <c r="C548" s="3">
         <v>46238.325694444444</v>
       </c>
-      <c r="D548" s="6" t="s">
-        <v>594</v>
+      <c r="D548" s="4" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="549" spans="2:4">
@@ -8613,8 +8851,8 @@
       <c r="C549" s="3">
         <v>46238.571527777778</v>
       </c>
-      <c r="D549" s="6" t="s">
-        <v>599</v>
+      <c r="D549" s="4" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="550" spans="2:4">
@@ -8624,8 +8862,8 @@
       <c r="C550" s="3">
         <v>46239.586805555555</v>
       </c>
-      <c r="D550" s="6" t="s">
-        <v>600</v>
+      <c r="D550" s="4" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="551" spans="2:4">
@@ -8635,8 +8873,8 @@
       <c r="C551" s="3">
         <v>46240.491666666669</v>
       </c>
-      <c r="D551" s="6" t="s">
-        <v>601</v>
+      <c r="D551" s="4" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="552" spans="2:4">
@@ -8646,8 +8884,8 @@
       <c r="C552" s="3">
         <v>46240.517361111109</v>
       </c>
-      <c r="D552" s="6" t="s">
-        <v>602</v>
+      <c r="D552" s="4" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="553" spans="2:4">
@@ -8657,8 +8895,8 @@
       <c r="C553" s="3">
         <v>46241.340277777781</v>
       </c>
-      <c r="D553" s="6" t="s">
-        <v>603</v>
+      <c r="D553" s="4" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="554" spans="2:4">
@@ -8668,19 +8906,19 @@
       <c r="C554" s="3">
         <v>46241.416666666664</v>
       </c>
-      <c r="D554" s="6" t="s">
-        <v>597</v>
+      <c r="D554" s="4" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="555" spans="2:4">
       <c r="B555" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C555" s="3">
         <v>46241.51458333333</v>
       </c>
-      <c r="D555" s="6" t="s">
-        <v>604</v>
+      <c r="D555" s="4" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="556" spans="2:4">
@@ -8690,8 +8928,8 @@
       <c r="C556" s="3">
         <v>46241.670138888891</v>
       </c>
-      <c r="D556" s="6" t="s">
-        <v>603</v>
+      <c r="D556" s="4" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="557" spans="2:4">
@@ -8701,8 +8939,8 @@
       <c r="C557" s="3">
         <v>46242.579861111109</v>
       </c>
-      <c r="D557" s="6" t="s">
-        <v>605</v>
+      <c r="D557" s="4" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="558" spans="2:4">
@@ -8712,8 +8950,8 @@
       <c r="C558" s="3">
         <v>46242.729166666664</v>
       </c>
-      <c r="D558" s="6" t="s">
-        <v>594</v>
+      <c r="D558" s="4" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="559" spans="2:4">
@@ -8723,8 +8961,8 @@
       <c r="C559" s="3">
         <v>46242.729166666664</v>
       </c>
-      <c r="D559" s="6" t="s">
-        <v>594</v>
+      <c r="D559" s="4" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="560" spans="2:4">
@@ -8734,19 +8972,19 @@
       <c r="C560" s="3">
         <v>46242.759027777778</v>
       </c>
-      <c r="D560" s="6" t="s">
-        <v>606</v>
+      <c r="D560" s="4" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="561" spans="2:4">
       <c r="B561" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C561" s="3">
         <v>46243.291666666664</v>
       </c>
-      <c r="D561" s="6" t="s">
-        <v>607</v>
+      <c r="D561" s="4" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="562" spans="2:4">
@@ -8756,8 +8994,8 @@
       <c r="C562" s="3">
         <v>46243.614583333336</v>
       </c>
-      <c r="D562" s="6" t="s">
-        <v>603</v>
+      <c r="D562" s="4" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="563" spans="2:4">
@@ -8767,8 +9005,8 @@
       <c r="C563" s="3">
         <v>46243.642361111109</v>
       </c>
-      <c r="D563" s="6" t="s">
-        <v>608</v>
+      <c r="D563" s="4" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="564" spans="2:4">
@@ -8778,8 +9016,8 @@
       <c r="C564" s="3">
         <v>46243.942361111112</v>
       </c>
-      <c r="D564" s="6" t="s">
-        <v>594</v>
+      <c r="D564" s="4" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="565" spans="2:4">
@@ -8789,8 +9027,8 @@
       <c r="C565" s="3">
         <v>46243.942361111112</v>
       </c>
-      <c r="D565" s="6" t="s">
-        <v>594</v>
+      <c r="D565" s="4" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="566" spans="2:4">
@@ -8800,8 +9038,8 @@
       <c r="C566" s="3">
         <v>46244.413194444445</v>
       </c>
-      <c r="D566" s="6" t="s">
-        <v>609</v>
+      <c r="D566" s="4" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="567" spans="2:4">
@@ -8811,8 +9049,8 @@
       <c r="C567" s="3">
         <v>46244.413194444445</v>
       </c>
-      <c r="D567" s="6" t="s">
-        <v>609</v>
+      <c r="D567" s="4" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="568" spans="2:4">
@@ -8822,8 +9060,8 @@
       <c r="C568" s="3">
         <v>46244.951388888891</v>
       </c>
-      <c r="D568" s="6" t="s">
-        <v>592</v>
+      <c r="D568" s="4" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="569" spans="2:4">
@@ -8833,30 +9071,30 @@
       <c r="C569" s="3">
         <v>46245.40625</v>
       </c>
-      <c r="D569" s="6" t="s">
-        <v>592</v>
+      <c r="D569" s="4" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="570" spans="2:4">
       <c r="B570" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C570" s="3">
         <v>46245.479166666664</v>
       </c>
-      <c r="D570" s="6" t="s">
-        <v>608</v>
+      <c r="D570" s="4" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="571" spans="2:4">
       <c r="B571" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C571" s="3">
         <v>46245.522222222222</v>
       </c>
-      <c r="D571" s="6" t="s">
-        <v>610</v>
+      <c r="D571" s="4" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="572" spans="2:4">
@@ -8866,8 +9104,8 @@
       <c r="C572" s="3">
         <v>46247.347222222219</v>
       </c>
-      <c r="D572" s="6" t="s">
-        <v>594</v>
+      <c r="D572" s="4" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="573" spans="2:4">
@@ -8877,8 +9115,8 @@
       <c r="C573" s="3">
         <v>46247.347222222219</v>
       </c>
-      <c r="D573" s="6" t="s">
-        <v>594</v>
+      <c r="D573" s="4" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="574" spans="2:4">
@@ -8888,8 +9126,8 @@
       <c r="C574" s="3">
         <v>46247.440972222219</v>
       </c>
-      <c r="D574" s="6" t="s">
-        <v>603</v>
+      <c r="D574" s="4" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="575" spans="2:4">
@@ -8899,8 +9137,8 @@
       <c r="C575" s="3">
         <v>46248.30972222222</v>
       </c>
-      <c r="D575" s="6" t="s">
-        <v>599</v>
+      <c r="D575" s="4" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="576" spans="2:4">
@@ -8910,19 +9148,19 @@
       <c r="C576" s="3">
         <v>46249.361111111109</v>
       </c>
-      <c r="D576" s="6" t="s">
-        <v>611</v>
+      <c r="D576" s="4" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="577" spans="2:4">
       <c r="B577" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C577" s="3">
         <v>46249.607638888891</v>
       </c>
-      <c r="D577" s="6" t="s">
-        <v>604</v>
+      <c r="D577" s="4" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="578" spans="2:4">
@@ -8932,8 +9170,8 @@
       <c r="C578" s="3">
         <v>46250.541666666664</v>
       </c>
-      <c r="D578" s="6" t="s">
-        <v>612</v>
+      <c r="D578" s="4" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="579" spans="2:4">
@@ -8943,8 +9181,8 @@
       <c r="C579" s="3">
         <v>46252.458333333336</v>
       </c>
-      <c r="D579" s="6" t="s">
-        <v>613</v>
+      <c r="D579" s="4" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="580" spans="2:4">
@@ -8954,8 +9192,8 @@
       <c r="C580" s="3">
         <v>46252.460416666669</v>
       </c>
-      <c r="D580" s="6" t="s">
-        <v>594</v>
+      <c r="D580" s="4" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="581" spans="2:4">
@@ -8965,8 +9203,8 @@
       <c r="C581" s="3">
         <v>46252.460416666669</v>
       </c>
-      <c r="D581" s="6" t="s">
-        <v>594</v>
+      <c r="D581" s="4" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="582" spans="2:4">
@@ -8976,8 +9214,8 @@
       <c r="C582" s="3">
         <v>46252.552083333336</v>
       </c>
-      <c r="D582" s="6" t="s">
-        <v>614</v>
+      <c r="D582" s="4" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="583" spans="2:4">
@@ -8987,20 +9225,15 @@
       <c r="C583" s="3">
         <v>46253.229166666664</v>
       </c>
-      <c r="D583" s="6" t="s">
-        <v>594</v>
+      <c r="D583" s="4" t="s">
+        <v>676</v>
       </c>
     </row>
     <row r="584" spans="2:4">
       <c r="B584" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C584" s="3">
-        <v>46253.447916666664</v>
-      </c>
-      <c r="D584" s="6" t="s">
-        <v>615</v>
-      </c>
+      <c r="D584" s="4"/>
     </row>
     <row r="585" spans="2:4">
       <c r="B585" s="1" t="s">
@@ -9009,8 +9242,8 @@
       <c r="C585" s="3">
         <v>46253.447916666664</v>
       </c>
-      <c r="D585" s="6" t="s">
-        <v>615</v>
+      <c r="D585" s="4" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="586" spans="2:4">
@@ -9020,8 +9253,8 @@
       <c r="C586" s="3">
         <v>46253.583333333336</v>
       </c>
-      <c r="D586" s="6" t="s">
-        <v>616</v>
+      <c r="D586" s="4" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="587" spans="2:4">
@@ -9031,8 +9264,8 @@
       <c r="C587" s="3">
         <v>46254.427083333336</v>
       </c>
-      <c r="D587" s="6" t="s">
-        <v>617</v>
+      <c r="D587" s="4" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="588" spans="2:4">
@@ -9042,8 +9275,8 @@
       <c r="C588" s="3">
         <v>46254.576388888891</v>
       </c>
-      <c r="D588" s="6" t="s">
-        <v>618</v>
+      <c r="D588" s="4" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="589" spans="2:4">
@@ -9053,8 +9286,8 @@
       <c r="C589" s="3">
         <v>46254.708333333336</v>
       </c>
-      <c r="D589" s="6" t="s">
-        <v>619</v>
+      <c r="D589" s="4" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="590" spans="2:4">
@@ -9064,8 +9297,8 @@
       <c r="C590" s="3">
         <v>46255.3125</v>
       </c>
-      <c r="D590" s="6" t="s">
-        <v>615</v>
+      <c r="D590" s="4" t="s">
+        <v>682</v>
       </c>
     </row>
     <row r="591" spans="2:4">
@@ -9075,8 +9308,8 @@
       <c r="C591" s="3">
         <v>46255.548611111109</v>
       </c>
-      <c r="D591" s="6" t="s">
-        <v>615</v>
+      <c r="D591" s="4" t="s">
+        <v>683</v>
       </c>
     </row>
     <row r="592" spans="2:4">
@@ -9086,8 +9319,8 @@
       <c r="C592" s="3">
         <v>46256.088194444441</v>
       </c>
-      <c r="D592" s="6" t="s">
-        <v>592</v>
+      <c r="D592" s="4" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="593" spans="2:4">
@@ -9097,8 +9330,8 @@
       <c r="C593" s="3">
         <v>46256.394444444442</v>
       </c>
-      <c r="D593" s="6" t="s">
-        <v>620</v>
+      <c r="D593" s="4" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="594" spans="2:4">
@@ -9108,8 +9341,8 @@
       <c r="C594" s="3">
         <v>46257.40347222222</v>
       </c>
-      <c r="D594" s="6" t="s">
-        <v>621</v>
+      <c r="D594" s="4" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="595" spans="2:4">
@@ -9119,8 +9352,8 @@
       <c r="C595" s="3">
         <v>46257.40347222222</v>
       </c>
-      <c r="D595" s="6" t="s">
-        <v>621</v>
+      <c r="D595" s="4" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="596" spans="2:4">
@@ -9130,8 +9363,8 @@
       <c r="C596" s="3">
         <v>46257.534722222219</v>
       </c>
-      <c r="D596" s="6" t="s">
-        <v>622</v>
+      <c r="D596" s="4" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="597" spans="2:4">
@@ -9141,8 +9374,8 @@
       <c r="C597" s="3">
         <v>46257.638888888891</v>
       </c>
-      <c r="D597" s="6" t="s">
-        <v>621</v>
+      <c r="D597" s="4" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="598" spans="2:4">
@@ -9152,8 +9385,8 @@
       <c r="C598" s="3">
         <v>46257.913888888892</v>
       </c>
-      <c r="D598" s="6" t="s">
-        <v>594</v>
+      <c r="D598" s="4" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="599" spans="2:4">
@@ -9163,8 +9396,8 @@
       <c r="C599" s="3">
         <v>46257.913888888892</v>
       </c>
-      <c r="D599" s="6" t="s">
-        <v>594</v>
+      <c r="D599" s="4" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="600" spans="2:4">
@@ -9174,8 +9407,8 @@
       <c r="C600" s="3">
         <v>46258.494664351849</v>
       </c>
-      <c r="D600" s="6" t="s">
-        <v>608</v>
+      <c r="D600" s="4" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="601" spans="2:4">
@@ -9185,8 +9418,8 @@
       <c r="C601" s="3">
         <v>46259.371527777781</v>
       </c>
-      <c r="D601" s="6" t="s">
-        <v>608</v>
+      <c r="D601" s="4" t="s">
+        <v>691</v>
       </c>
     </row>
     <row r="602" spans="2:4">
@@ -9196,19 +9429,19 @@
       <c r="C602" s="3">
         <v>46259.390972222223</v>
       </c>
-      <c r="D602" s="6" t="s">
-        <v>617</v>
+      <c r="D602" s="4" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="603" spans="2:4">
       <c r="B603" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C603" s="3">
         <v>46259.545138888891</v>
       </c>
-      <c r="D603" s="6" t="s">
-        <v>623</v>
+      <c r="D603" s="4" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="604" spans="2:4">
@@ -9218,8 +9451,8 @@
       <c r="C604" s="3">
         <v>46259.5625</v>
       </c>
-      <c r="D604" s="6" t="s">
-        <v>594</v>
+      <c r="D604" s="4" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="605" spans="2:4">
@@ -9229,8 +9462,8 @@
       <c r="C605" s="3">
         <v>46259.5625</v>
       </c>
-      <c r="D605" s="6" t="s">
-        <v>594</v>
+      <c r="D605" s="4" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="606" spans="2:4">
@@ -9240,8 +9473,8 @@
       <c r="C606" s="3">
         <v>46260.739583333336</v>
       </c>
-      <c r="D606" s="6" t="s">
-        <v>624</v>
+      <c r="D606" s="4" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="607" spans="2:4">
@@ -9251,8 +9484,8 @@
       <c r="C607" s="3">
         <v>46261.262499999997</v>
       </c>
-      <c r="D607" s="6" t="s">
-        <v>608</v>
+      <c r="D607" s="4" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="608" spans="2:4">
@@ -9262,8 +9495,8 @@
       <c r="C608" s="3">
         <v>46261.291666666664</v>
       </c>
-      <c r="D608" s="6" t="s">
-        <v>625</v>
+      <c r="D608" s="4" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="609" spans="2:4">
@@ -9273,8 +9506,8 @@
       <c r="C609" s="3">
         <v>46261.291666666664</v>
       </c>
-      <c r="D609" s="6" t="s">
-        <v>626</v>
+      <c r="D609" s="4" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="610" spans="2:4">
@@ -9284,19 +9517,19 @@
       <c r="C610" s="3">
         <v>46261.340277777781</v>
       </c>
-      <c r="D610" s="6" t="s">
-        <v>592</v>
+      <c r="D610" s="4" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="611" spans="2:4">
       <c r="B611" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C611" s="3">
         <v>46261.444444444445</v>
       </c>
-      <c r="D611" s="6" t="s">
-        <v>627</v>
+      <c r="D611" s="4" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="612" spans="2:4">
@@ -9306,8 +9539,8 @@
       <c r="C612" s="3">
         <v>46261.5</v>
       </c>
-      <c r="D612" s="6" t="s">
-        <v>628</v>
+      <c r="D612" s="4" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="613" spans="2:4">
@@ -9317,8 +9550,8 @@
       <c r="C613" s="3">
         <v>46261.722222222219</v>
       </c>
-      <c r="D613" s="6" t="s">
-        <v>624</v>
+      <c r="D613" s="4" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="614" spans="2:4">
@@ -9328,8 +9561,8 @@
       <c r="C614" s="3">
         <v>46262.118055555555</v>
       </c>
-      <c r="D614" s="6" t="s">
-        <v>613</v>
+      <c r="D614" s="4" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="615" spans="2:4">
@@ -9339,8 +9572,8 @@
       <c r="C615" s="3">
         <v>46262.25</v>
       </c>
-      <c r="D615" s="6" t="s">
-        <v>629</v>
+      <c r="D615" s="4" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="616" spans="2:4">
@@ -9350,19 +9583,19 @@
       <c r="C616" s="3">
         <v>46262.427083333336</v>
       </c>
-      <c r="D616" s="6" t="s">
-        <v>618</v>
+      <c r="D616" s="4" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="617" spans="2:4">
       <c r="B617" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C617" s="3">
         <v>46262.50277777778</v>
       </c>
-      <c r="D617" s="6" t="s">
-        <v>614</v>
+      <c r="D617" s="4" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="618" spans="2:4">
@@ -9372,8 +9605,8 @@
       <c r="C618" s="3">
         <v>46263.194444444445</v>
       </c>
-      <c r="D618" s="6" t="s">
-        <v>594</v>
+      <c r="D618" s="4" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="619" spans="2:4">
@@ -9383,8 +9616,8 @@
       <c r="C619" s="3">
         <v>46263.194444444445</v>
       </c>
-      <c r="D619" s="6" t="s">
-        <v>594</v>
+      <c r="D619" s="4" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="620" spans="2:4">
@@ -9394,8 +9627,8 @@
       <c r="C620" s="3">
         <v>46263.739583333336</v>
       </c>
-      <c r="D620" s="6" t="s">
-        <v>615</v>
+      <c r="D620" s="4" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="621" spans="2:4">
@@ -9405,8 +9638,8 @@
       <c r="C621" s="3">
         <v>46264.333333333336</v>
       </c>
-      <c r="D621" s="6" t="s">
-        <v>630</v>
+      <c r="D621" s="4" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="622" spans="2:4">
@@ -9416,8 +9649,8 @@
       <c r="C622" s="3">
         <v>46264.708333333336</v>
       </c>
-      <c r="D622" s="6" t="s">
-        <v>631</v>
+      <c r="D622" s="4" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="623" spans="2:4">
@@ -9427,8 +9660,8 @@
       <c r="C623" s="3">
         <v>46265.25</v>
       </c>
-      <c r="D623" s="6" t="s">
-        <v>594</v>
+      <c r="D623" s="4" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="624" spans="2:4">
@@ -9438,8 +9671,8 @@
       <c r="C624" s="3">
         <v>46265.25</v>
       </c>
-      <c r="D624" s="6" t="s">
-        <v>594</v>
+      <c r="D624" s="4" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="625" spans="2:4">
@@ -9449,8 +9682,8 @@
       <c r="C625" s="3">
         <v>46265.291666666664</v>
       </c>
-      <c r="D625" s="6" t="s">
-        <v>632</v>
+      <c r="D625" s="4" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="626" spans="2:4">
@@ -9460,19 +9693,19 @@
       <c r="C626" s="3">
         <v>46265.569444444445</v>
       </c>
-      <c r="D626" s="6" t="s">
-        <v>633</v>
+      <c r="D626" s="4" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="627" spans="2:4">
       <c r="B627" s="1" t="s">
-        <v>581</v>
+        <v>7</v>
       </c>
       <c r="C627" s="3">
         <v>46265.59375</v>
       </c>
-      <c r="D627" s="6" t="s">
-        <v>634</v>
+      <c r="D627" s="4" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="628" spans="2:4">
@@ -9482,8 +9715,8 @@
       <c r="C628" s="3">
         <v>46265.631944444445</v>
       </c>
-      <c r="D628" s="6" t="s">
-        <v>635</v>
+      <c r="D628" s="4" t="s">
+        <v>713</v>
       </c>
     </row>
     <row r="629" spans="2:4">
@@ -9493,8 +9726,8 @@
       <c r="C629" s="3">
         <v>46265.69027777778</v>
       </c>
-      <c r="D629" s="6" t="s">
-        <v>608</v>
+      <c r="D629" s="4" t="s">
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -9507,6 +9740,880 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824CD0BE-F8A6-4630-BBC6-A47FE782D458}">
+  <dimension ref="D2:F79"/>
+  <sheetFormatPr defaultColWidth="243.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="155.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:6" ht="15">
+      <c r="D2" s="29" t="s">
+        <v>576</v>
+      </c>
+      <c r="E2" s="35">
+        <v>46237.208333333336</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="3" spans="4:6" ht="15">
+      <c r="D3" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="E3" s="35">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="4" spans="4:6" ht="15">
+      <c r="D4" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="35">
+        <v>46237.263888888891</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="5" spans="4:6" ht="15">
+      <c r="D5" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="35">
+        <v>46237.40625</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="6" spans="4:6" ht="15">
+      <c r="D6" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="35">
+        <v>46237.434027777781</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="7" spans="4:6" ht="15">
+      <c r="D7" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="E7" s="35">
+        <v>46237.749305555553</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="8" spans="4:6" ht="15">
+      <c r="D8" s="29" t="s">
+        <v>578</v>
+      </c>
+      <c r="E8" s="35">
+        <v>46238.28402777778</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="9" spans="4:6" ht="15">
+      <c r="D9" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="E9" s="35">
+        <v>46238.325694444444</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="10" spans="4:6" ht="15">
+      <c r="D10" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="E10" s="35">
+        <v>46238.571527777778</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="11" spans="4:6" ht="15">
+      <c r="D11" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="35">
+        <v>46239.586805555555</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="12" spans="4:6" ht="15">
+      <c r="D12" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="37">
+        <v>46240.491666666669</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="13" spans="4:6" ht="30">
+      <c r="D13" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="37">
+        <v>46240.517361111109</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="14" spans="4:6" ht="15">
+      <c r="D14" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="E14" s="37">
+        <v>46241.340277777781</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="15" spans="4:6" ht="15">
+      <c r="D15" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="E15" s="37">
+        <v>46241.416666666664</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="16" spans="4:6" ht="15">
+      <c r="D16" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E16" s="37">
+        <v>46241.51458333333</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" ht="15">
+      <c r="D17" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="E17" s="37">
+        <v>46241.670138888891</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" ht="15">
+      <c r="D18" s="30" t="s">
+        <v>582</v>
+      </c>
+      <c r="E18" s="37">
+        <v>46242.579861111109</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" ht="15">
+      <c r="D19" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E19" s="37">
+        <v>46242.729166666664</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" ht="15">
+      <c r="D20" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="37">
+        <v>46242.759027777778</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" ht="15">
+      <c r="D21" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E21" s="37">
+        <v>46243.291666666664</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" ht="15">
+      <c r="D22" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E22" s="37">
+        <v>46243.614583333336</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" ht="15">
+      <c r="D23" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="E23" s="37">
+        <v>46243.642361111109</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" ht="15">
+      <c r="D24" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E24" s="37">
+        <v>46243.942361111112</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" ht="15">
+      <c r="D25" s="30" t="s">
+        <v>584</v>
+      </c>
+      <c r="E25" s="37">
+        <v>46244.413194444445</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" ht="15">
+      <c r="D26" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="E26" s="37">
+        <v>46244.951388888891</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" ht="15">
+      <c r="D27" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="E27" s="37">
+        <v>46245.40625</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="15">
+      <c r="D28" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E28" s="37">
+        <v>46245.479166666664</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" ht="15">
+      <c r="D29" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E29" s="37">
+        <v>46245.522222222222</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" ht="15">
+      <c r="D30" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E30" s="37">
+        <v>46247.347222222219</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="31" spans="4:6" ht="15">
+      <c r="D31" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E31" s="37">
+        <v>46247.440972222219</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" ht="15">
+      <c r="D32" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="E32" s="37">
+        <v>46248.30972222222</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="33" spans="4:6" ht="15">
+      <c r="D33" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="E33" s="37">
+        <v>46249.361111111109</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="34" spans="4:6" ht="15">
+      <c r="D34" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E34" s="37">
+        <v>46249.607638888891</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="35" spans="4:6" ht="15">
+      <c r="D35" s="30" t="s">
+        <v>577</v>
+      </c>
+      <c r="E35" s="37">
+        <v>46250.541666666664</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="36" spans="4:6" ht="15">
+      <c r="D36" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="E36" s="37">
+        <v>46252.458333333336</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="37" spans="4:6" ht="15">
+      <c r="D37" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E37" s="37">
+        <v>46252.460416666669</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="38" spans="4:6" ht="15">
+      <c r="D38" s="30" t="s">
+        <v>582</v>
+      </c>
+      <c r="E38" s="37">
+        <v>46252.552083333336</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="39" spans="4:6" ht="15">
+      <c r="D39" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="37">
+        <v>46253.229166666664</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="40" spans="4:6" ht="15">
+      <c r="D40" s="30" t="s">
+        <v>587</v>
+      </c>
+      <c r="E40" s="37">
+        <v>46253.447916666664</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="41" spans="4:6" ht="15">
+      <c r="D41" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="37">
+        <v>46253.583333333336</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="42" spans="4:6" ht="15">
+      <c r="D42" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="37">
+        <v>46254.427083333336</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="43" spans="4:6" ht="15">
+      <c r="D43" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="37">
+        <v>46254.576388888891</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="44" spans="4:6" ht="15">
+      <c r="D44" s="30" t="s">
+        <v>588</v>
+      </c>
+      <c r="E44" s="37">
+        <v>46254.708333333336</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="45" spans="4:6" ht="15">
+      <c r="D45" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="37">
+        <v>46255.3125</v>
+      </c>
+      <c r="F45" s="42" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="46" spans="4:6" ht="15">
+      <c r="D46" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="37">
+        <v>46255.548611111109</v>
+      </c>
+      <c r="F46" s="42" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="47" spans="4:6" ht="15">
+      <c r="D47" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="E47" s="37">
+        <v>46256.088194444441</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="48" spans="4:6" ht="15">
+      <c r="D48" s="30" t="s">
+        <v>589</v>
+      </c>
+      <c r="E48" s="37">
+        <v>46256.394444444442</v>
+      </c>
+      <c r="F48" s="42" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="49" spans="4:6" ht="15">
+      <c r="D49" s="30" t="s">
+        <v>578</v>
+      </c>
+      <c r="E49" s="37">
+        <v>46257.40347222222</v>
+      </c>
+      <c r="F49" s="42" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="50" spans="4:6" ht="15">
+      <c r="D50" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="E50" s="37">
+        <v>46257.534722222219</v>
+      </c>
+      <c r="F50" s="42" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="51" spans="4:6" ht="15">
+      <c r="D51" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E51" s="37">
+        <v>46257.638888888891</v>
+      </c>
+      <c r="F51" s="42" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="52" spans="4:6" ht="15">
+      <c r="D52" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E52" s="37">
+        <v>46257.913888888892</v>
+      </c>
+      <c r="F52" s="42" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="53" spans="4:6" ht="15">
+      <c r="D53" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="E53" s="37">
+        <v>46258.494664351849</v>
+      </c>
+      <c r="F53" s="42" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="54" spans="4:6" ht="15">
+      <c r="D54" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="E54" s="37">
+        <v>46259.371527777781</v>
+      </c>
+      <c r="F54" s="42" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="55" spans="4:6" ht="15">
+      <c r="D55" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="E55" s="37">
+        <v>46259.390972222223</v>
+      </c>
+      <c r="F55" s="42" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="56" spans="4:6" ht="15">
+      <c r="D56" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E56" s="37">
+        <v>46259.545138888891</v>
+      </c>
+      <c r="F56" s="42" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="57" spans="4:6" ht="15">
+      <c r="D57" s="30" t="s">
+        <v>579</v>
+      </c>
+      <c r="E57" s="37">
+        <v>46259.5625</v>
+      </c>
+      <c r="F57" s="42" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="58" spans="4:6" ht="15">
+      <c r="D58" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E58" s="37">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="F58" s="42" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="59" spans="4:6" ht="15">
+      <c r="D59" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E59" s="37">
+        <v>46261.262499999997</v>
+      </c>
+      <c r="F59" s="42" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="60" spans="4:6" ht="15">
+      <c r="D60" s="30" t="s">
+        <v>589</v>
+      </c>
+      <c r="E60" s="37">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="61" spans="4:6" ht="15">
+      <c r="D61" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E61" s="37">
+        <v>46261.291666666664</v>
+      </c>
+      <c r="F61" s="42" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="62" spans="4:6" ht="15">
+      <c r="D62" s="30" t="s">
+        <v>576</v>
+      </c>
+      <c r="E62" s="37">
+        <v>46261.340277777781</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="63" spans="4:6" ht="15">
+      <c r="D63" s="30" t="s">
+        <v>581</v>
+      </c>
+      <c r="E63" s="37">
+        <v>46261.444444444445</v>
+      </c>
+      <c r="F63" s="42" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="64" spans="4:6" ht="15">
+      <c r="D64" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="E64" s="35">
+        <v>46261.5</v>
+      </c>
+      <c r="F64" s="41" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="65" spans="4:6" ht="15">
+      <c r="D65" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E65" s="37">
+        <v>46261.722222222219</v>
+      </c>
+      <c r="F65" s="42" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="66" spans="4:6" ht="15">
+      <c r="D66" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="E66" s="35">
+        <v>46262.118055555555</v>
+      </c>
+      <c r="F66" s="41" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="67" spans="4:6" ht="15">
+      <c r="D67" s="30" t="s">
+        <v>583</v>
+      </c>
+      <c r="E67" s="35">
+        <v>46262.25</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="68" spans="4:6" ht="15">
+      <c r="D68" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E68" s="35">
+        <v>46262.427083333336</v>
+      </c>
+      <c r="F68" s="41" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="69" spans="4:6" ht="15">
+      <c r="D69" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="E69" s="35">
+        <v>46262.50277777778</v>
+      </c>
+      <c r="F69" s="41" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="70" spans="4:6" ht="15">
+      <c r="D70" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="E70" s="35">
+        <v>46263.194444444445</v>
+      </c>
+      <c r="F70" s="41" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="71" spans="4:6" ht="15">
+      <c r="D71" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="E71" s="35">
+        <v>46263.739583333336</v>
+      </c>
+      <c r="F71" s="41" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="72" spans="4:6" ht="15">
+      <c r="D72" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="35">
+        <v>46264.333333333336</v>
+      </c>
+      <c r="F72" s="41" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="73" spans="4:6" ht="15">
+      <c r="D73" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="E73" s="35">
+        <v>46264.708333333336</v>
+      </c>
+      <c r="F73" s="41" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="74" spans="4:6" ht="15">
+      <c r="D74" s="29" t="s">
+        <v>579</v>
+      </c>
+      <c r="E74" s="35">
+        <v>46265.25</v>
+      </c>
+      <c r="F74" s="41" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="75" spans="4:6" ht="15">
+      <c r="D75" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="35">
+        <v>46265.291666666664</v>
+      </c>
+      <c r="F75" s="41" t="e">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="76" spans="4:6" ht="15">
+      <c r="D76" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="35">
+        <v>46265.569444444445</v>
+      </c>
+      <c r="F76" s="41" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="77" spans="4:6" ht="15">
+      <c r="D77" s="29" t="s">
+        <v>581</v>
+      </c>
+      <c r="E77" s="35">
+        <v>46265.59375</v>
+      </c>
+      <c r="F77" s="41" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="78" spans="4:6" ht="15">
+      <c r="D78" s="32" t="s">
+        <v>582</v>
+      </c>
+      <c r="E78" s="35">
+        <v>46265.631944444445</v>
+      </c>
+      <c r="F78" s="41" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="79" spans="4:6" ht="15">
+      <c r="D79" s="29" t="s">
+        <v>583</v>
+      </c>
+      <c r="E79" s="35">
+        <v>46265.69027777778</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>714</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B82532-6694-4B08-9527-A22A4CBED7A9}">
   <dimension ref="B2:K68"/>
   <sheetFormatPr defaultColWidth="40.44140625" defaultRowHeight="14.4"/>
@@ -11665,7 +12772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F4E357-577A-48CD-A40C-9C0C2C5D09D3}">
   <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -11677,1560 +12784,1560 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C1" s="36">
+      <c r="C1" s="35">
         <v>46237.208333333336</v>
       </c>
-      <c r="D1" s="36">
+      <c r="D1" s="35">
         <v>46237.302083333336</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F1" s="33" t="s">
+      <c r="E1" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1" s="32" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C2" s="36">
+      <c r="C2" s="35">
         <v>46237.263888888891</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="35">
         <v>46237.395833333336</v>
       </c>
-      <c r="E2" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F2" s="33" t="s">
+      <c r="E2" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F2" s="32" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="35">
         <v>46237.263888888891</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="35">
         <v>46237.597222222219</v>
       </c>
-      <c r="E3" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F3" s="33" t="s">
+      <c r="E3" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F3" s="32" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="35">
         <v>46237.40625</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="35">
         <v>46237.416666666664</v>
       </c>
-      <c r="E4" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F4" s="32" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="35">
         <v>46237.434027777781</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="35">
         <v>46237.458333333336</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="E5" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F5" s="32" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="35">
         <v>46237.749305555553</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="35">
         <v>46237.756944444445</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F6" s="33" t="s">
+      <c r="E6" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F6" s="32" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="35">
         <v>46238.28402777778</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="35">
         <v>46238.287499999999</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F7" s="33" t="s">
+      <c r="E7" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F7" s="32" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="35">
         <v>46238.325694444444</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="35">
         <v>46238.345833333333</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F8" s="33" t="s">
+      <c r="E8" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F8" s="32" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="35">
         <v>46238.571527777778</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="35">
         <v>46238.573611111111</v>
       </c>
-      <c r="E9" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F9" s="30" t="s">
+      <c r="E9" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="35">
         <v>46239.586805555555</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="35">
         <v>46241.576388888891</v>
       </c>
-      <c r="E10" s="37" t="s">
-        <v>477</v>
-      </c>
-      <c r="F10" s="33" t="s">
+      <c r="E10" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F10" s="32" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="37">
         <v>46240.491666666669</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="37">
         <v>46240.736805555556</v>
       </c>
-      <c r="E11" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F11" s="34" t="s">
+      <c r="E11" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="37">
         <v>46240.517361111109</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="37">
         <v>46241.316666666666</v>
       </c>
-      <c r="E12" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F12" s="34" t="s">
+      <c r="E12" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F12" s="33" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="37">
         <v>46241.340277777781</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="37">
         <v>46241.361111111109</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F13" s="34" t="s">
+      <c r="E13" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="37">
         <v>46241.416666666664</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="37">
         <v>46241.419444444444</v>
       </c>
-      <c r="E14" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F14" s="34" t="s">
+      <c r="E14" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="37">
         <v>46241.51458333333</v>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="37">
         <v>46241.519444444442</v>
       </c>
-      <c r="E15" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F15" s="34" t="s">
+      <c r="E15" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="37">
         <v>46241.670138888891</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="37">
         <v>46241.677777777775</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F16" s="34" t="s">
+      <c r="E16" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="30" t="s">
         <v>582</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="37">
         <v>46242.579861111109</v>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="37">
         <v>46242.631944444445</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="38">
         <v>0.58333333333333337</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="33" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="37">
         <v>46242.729166666664</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="37">
         <v>46243.333333333336</v>
       </c>
-      <c r="E18" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F18" s="34" t="s">
+      <c r="E18" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F18" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="37">
         <v>46242.759027777778</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="37">
         <v>46243.291666666664</v>
       </c>
-      <c r="E19" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F19" s="34" t="s">
+      <c r="E19" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="37">
         <v>46243.291666666664</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="37">
         <v>46243.590277777781</v>
       </c>
-      <c r="E20" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F20" s="34" t="s">
+      <c r="E20" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="30" t="s">
         <v>637</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="37">
         <v>46243.614583333336</v>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="37">
         <v>46243.623611111114</v>
       </c>
-      <c r="E21" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F21" s="34" t="s">
+      <c r="E21" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="37">
         <v>46243.642361111109</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="37">
         <v>46243.651388888888</v>
       </c>
-      <c r="E22" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F22" s="34" t="s">
+      <c r="E22" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="37">
         <v>46243.942361111112</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D23" s="37">
         <v>46244.3125</v>
       </c>
-      <c r="E23" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F23" s="34" t="s">
+      <c r="E23" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="30" t="s">
         <v>584</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="37">
         <v>46244.413194444445</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="37">
         <v>46244.444444444445</v>
       </c>
-      <c r="E24" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F24" s="34" t="s">
+      <c r="E24" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F24" s="33" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="37">
         <v>46244.951388888891</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="37">
         <v>46244.326388888891</v>
       </c>
-      <c r="E25" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F25" s="34" t="s">
+      <c r="E25" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F25" s="33" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C26" s="38">
+      <c r="C26" s="37">
         <v>46245.40625</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="37">
         <v>46245.410416666666</v>
       </c>
-      <c r="E26" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F26" s="34" t="s">
+      <c r="E26" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F26" s="33" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="37">
         <v>46245.479166666664</v>
       </c>
-      <c r="D27" s="38">
+      <c r="D27" s="37">
         <v>46245.482638888891</v>
       </c>
-      <c r="E27" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F27" s="34" t="s">
+      <c r="E27" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F27" s="33" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="37">
         <v>46245.522222222222</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="37">
         <v>46245.524305555555</v>
       </c>
-      <c r="E28" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F28" s="34" t="s">
+      <c r="E28" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="37">
         <v>46247.347222222219</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="37">
         <v>46247.381944444445</v>
       </c>
-      <c r="E29" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F29" s="34" t="s">
+      <c r="E29" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="37">
         <v>46247.440972222219</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="37">
         <v>46247.447916666664</v>
       </c>
-      <c r="E30" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F30" s="34" t="s">
+      <c r="E30" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F30" s="33" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="30" t="s">
         <v>585</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="37">
         <v>46248.30972222222</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="37">
         <v>46248.311111111114</v>
       </c>
-      <c r="E31" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F31" s="34" t="s">
+      <c r="E31" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F31" s="33" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="30" t="s">
         <v>580</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="37">
         <v>46249.361111111109</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="37">
         <v>46254.375</v>
       </c>
-      <c r="E32" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="E32" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F32" s="33" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="37">
         <v>46249.607638888891</v>
       </c>
-      <c r="D33" s="38">
+      <c r="D33" s="37">
         <v>46249.612500000003</v>
       </c>
-      <c r="E33" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F33" s="34" t="s">
+      <c r="E33" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="30" t="s">
         <v>577</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="37">
         <v>46250.541666666664</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="37">
         <v>46250.601388888892</v>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="38">
         <v>0.5493055555555556</v>
       </c>
-      <c r="F34" s="34" t="s">
+      <c r="F34" s="33" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="30" t="s">
         <v>586</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C35" s="37">
         <v>46252.458333333336</v>
       </c>
-      <c r="D35" s="38">
+      <c r="D35" s="37">
         <v>46252.740972222222</v>
       </c>
-      <c r="E35" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F35" s="34" t="s">
+      <c r="E35" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F35" s="33" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C36" s="38">
+      <c r="C36" s="37">
         <v>46252.460416666669</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="37">
         <v>46252.630555555559</v>
       </c>
-      <c r="E36" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F36" s="34" t="s">
+      <c r="E36" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F36" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="30" t="s">
         <v>582</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="37">
         <v>46252.552083333336</v>
       </c>
-      <c r="D37" s="38">
+      <c r="D37" s="37">
         <v>46252.6875</v>
       </c>
-      <c r="E37" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F37" s="34" t="s">
+      <c r="E37" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F37" s="33" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="37">
         <v>46253.229166666664</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="37">
         <v>46253.361111111109</v>
       </c>
-      <c r="E38" s="39">
+      <c r="E38" s="38">
         <v>0.29166666666666669</v>
       </c>
-      <c r="F38" s="34" t="s">
+      <c r="F38" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="31" t="s">
         <v>587</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>636</v>
       </c>
-      <c r="C39" s="40">
+      <c r="C39" s="39">
         <v>46253.447916666664</v>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="39">
         <v>46255.381944444445</v>
       </c>
-      <c r="E39" s="41" t="s">
-        <v>477</v>
-      </c>
-      <c r="F39" s="35" t="s">
+      <c r="E39" s="40" t="s">
+        <v>477</v>
+      </c>
+      <c r="F39" s="34" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="37">
         <v>46253.583333333336</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="37">
         <v>46254.479166666664</v>
       </c>
-      <c r="E40" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F40" s="34" t="s">
+      <c r="E40" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C41" s="37">
         <v>46254.427083333336</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="37">
         <v>46254.569444444445</v>
       </c>
-      <c r="E41" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F41" s="34" t="s">
+      <c r="E41" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F41" s="33" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="37">
         <v>46254.576388888891</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="37">
         <v>46254.893750000003</v>
       </c>
-      <c r="E42" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F42" s="34" t="s">
+      <c r="E42" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F42" s="33" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="30" t="s">
         <v>588</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C43" s="38">
+      <c r="C43" s="37">
         <v>46254.708333333336</v>
       </c>
-      <c r="D43" s="38" t="s">
-        <v>477</v>
-      </c>
-      <c r="E43" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F43" s="34" t="s">
+      <c r="D43" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F43" s="33" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15">
-      <c r="A44" s="31" t="s">
+      <c r="A44" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="37">
         <v>46255.3125</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="37">
         <v>46255.534722222219</v>
       </c>
-      <c r="E44" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F44" s="34" t="s">
+      <c r="E44" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F44" s="33" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15">
-      <c r="A45" s="31" t="s">
+      <c r="A45" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="37">
         <v>46255.548611111109</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="37">
         <v>46255.631944444445</v>
       </c>
-      <c r="E45" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F45" s="34" t="s">
+      <c r="E45" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F45" s="33" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15">
-      <c r="A46" s="31" t="s">
+      <c r="A46" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="37">
         <v>46256.088194444441</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="37">
         <v>46256.306944444441</v>
       </c>
-      <c r="E46" s="39"/>
-      <c r="F46" s="34" t="s">
+      <c r="E46" s="38"/>
+      <c r="F46" s="33" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="30" t="s">
         <v>589</v>
       </c>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="37">
         <v>46256.394444444442</v>
       </c>
-      <c r="D47" s="38">
+      <c r="D47" s="37">
         <v>46259.32916666667</v>
       </c>
-      <c r="E47" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F47" s="34" t="s">
+      <c r="E47" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F47" s="33" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15">
-      <c r="A48" s="31" t="s">
+      <c r="A48" s="30" t="s">
         <v>578</v>
       </c>
-      <c r="B48" s="31" t="s">
+      <c r="B48" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="37">
         <v>46257.40347222222</v>
       </c>
-      <c r="D48" s="38">
+      <c r="D48" s="37">
         <v>46257.408333333333</v>
       </c>
-      <c r="E48" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F48" s="34" t="s">
+      <c r="E48" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F48" s="33" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="30" t="s">
         <v>590</v>
       </c>
-      <c r="B49" s="31" t="s">
+      <c r="B49" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="37">
         <v>46257.534722222219</v>
       </c>
-      <c r="D49" s="38">
+      <c r="D49" s="37">
         <v>46257.59375</v>
       </c>
-      <c r="E49" s="39">
+      <c r="E49" s="38">
         <v>0.54166666666666663</v>
       </c>
-      <c r="F49" s="34" t="s">
+      <c r="F49" s="33" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="30" t="s">
         <v>637</v>
       </c>
-      <c r="C50" s="38">
+      <c r="C50" s="37">
         <v>46257.638888888891</v>
       </c>
-      <c r="D50" s="38">
+      <c r="D50" s="37">
         <v>46257.652777777781</v>
       </c>
-      <c r="E50" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F50" s="34" t="s">
+      <c r="E50" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F50" s="33" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B51" s="31" t="s">
+      <c r="B51" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C51" s="38">
+      <c r="C51" s="37">
         <v>46257.913888888892</v>
       </c>
-      <c r="D51" s="38">
+      <c r="D51" s="37">
         <v>46258.333333333336</v>
       </c>
-      <c r="E51" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F51" s="34" t="s">
+      <c r="E51" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F51" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="30" t="s">
         <v>586</v>
       </c>
-      <c r="B52" s="31" t="s">
+      <c r="B52" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C52" s="38">
+      <c r="C52" s="37">
         <v>46258.494664351849</v>
       </c>
-      <c r="D52" s="38">
+      <c r="D52" s="37">
         <v>46258.508888888886</v>
       </c>
-      <c r="E52" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F52" s="34" t="s">
+      <c r="E52" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F52" s="33" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="30" t="s">
         <v>586</v>
       </c>
-      <c r="B53" s="31" t="s">
+      <c r="B53" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C53" s="38">
+      <c r="C53" s="37">
         <v>46259.371527777781</v>
       </c>
-      <c r="D53" s="38">
+      <c r="D53" s="37">
         <v>46259.381249999999</v>
       </c>
-      <c r="E53" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F53" s="34" t="s">
+      <c r="E53" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F53" s="33" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="30" t="s">
         <v>586</v>
       </c>
-      <c r="B54" s="31" t="s">
+      <c r="B54" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C54" s="38">
+      <c r="C54" s="37">
         <v>46259.390972222223</v>
       </c>
-      <c r="D54" s="38">
+      <c r="D54" s="37">
         <v>46259.649305555555</v>
       </c>
-      <c r="E54" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F54" s="34" t="s">
+      <c r="E54" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F54" s="33" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B55" s="31" t="s">
+      <c r="B55" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C55" s="38">
+      <c r="C55" s="37">
         <v>46259.545138888891</v>
       </c>
-      <c r="D55" s="38">
+      <c r="D55" s="37">
         <v>46259.581250000003</v>
       </c>
-      <c r="E55" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F55" s="34" t="s">
+      <c r="E55" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F55" s="33" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C56" s="38">
+      <c r="C56" s="37">
         <v>46259.5625</v>
       </c>
-      <c r="D56" s="38">
+      <c r="D56" s="37">
         <v>46259.638888888891</v>
       </c>
-      <c r="E56" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F56" s="34" t="s">
+      <c r="E56" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F56" s="33" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="B57" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C57" s="38">
+      <c r="C57" s="37">
         <v>46260.739583333336</v>
       </c>
-      <c r="D57" s="38">
+      <c r="D57" s="37">
         <v>46261.095833333333</v>
       </c>
-      <c r="E57" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F57" s="34" t="s">
+      <c r="E57" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F57" s="33" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B58" s="31" t="s">
+      <c r="B58" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C58" s="38">
+      <c r="C58" s="37">
         <v>46261.262499999997</v>
       </c>
-      <c r="D58" s="38">
+      <c r="D58" s="37">
         <v>46261.277777777781</v>
       </c>
-      <c r="E58" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F58" s="34" t="s">
+      <c r="E58" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F58" s="33" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="30" t="s">
         <v>589</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="B59" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C59" s="38">
+      <c r="C59" s="37">
         <v>46261.291666666664</v>
       </c>
-      <c r="D59" s="38">
+      <c r="D59" s="37">
         <v>46261.340277777781</v>
       </c>
-      <c r="E59" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F59" s="34" t="s">
+      <c r="E59" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F59" s="33" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15">
-      <c r="A60" s="31" t="s">
+      <c r="A60" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B60" s="31" t="s">
+      <c r="B60" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C60" s="38">
+      <c r="C60" s="37">
         <v>46261.291666666664</v>
       </c>
-      <c r="D60" s="38">
+      <c r="D60" s="37">
         <v>46261.479166666664</v>
       </c>
-      <c r="E60" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F60" s="34" t="s">
+      <c r="E60" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F60" s="33" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="B61" s="31" t="s">
+      <c r="B61" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C61" s="37">
         <v>46261.340277777781</v>
       </c>
-      <c r="D61" s="38">
+      <c r="D61" s="37">
         <v>46261.379861111112</v>
       </c>
-      <c r="E61" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F61" s="34" t="s">
+      <c r="E61" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F61" s="33" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="37">
         <v>46261.444444444445</v>
       </c>
-      <c r="D62" s="38">
+      <c r="D62" s="37">
         <v>46261.493055555555</v>
       </c>
-      <c r="E62" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F62" s="34" t="s">
+      <c r="E62" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" s="33" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="29" t="s">
         <v>583</v>
       </c>
-      <c r="B63" s="31" t="s">
+      <c r="B63" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C63" s="36">
+      <c r="C63" s="35">
         <v>46261.5</v>
       </c>
-      <c r="D63" s="36">
+      <c r="D63" s="35">
         <v>46262.25</v>
       </c>
-      <c r="E63" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F63" s="34" t="s">
+      <c r="E63" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F63" s="33" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B64" s="31" t="s">
+      <c r="B64" s="30" t="s">
         <v>636</v>
       </c>
-      <c r="C64" s="38">
+      <c r="C64" s="37">
         <v>46261.722222222219</v>
       </c>
-      <c r="D64" s="38">
+      <c r="D64" s="37">
         <v>46262.170138888891</v>
       </c>
-      <c r="E64" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F64" s="34" t="s">
+      <c r="E64" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F64" s="33" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="B65" s="30" t="s">
+      <c r="B65" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="35">
         <v>46262.118055555555</v>
       </c>
-      <c r="D65" s="36">
+      <c r="D65" s="35">
         <v>46262.357638888891</v>
       </c>
-      <c r="E65" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F65" s="34" t="s">
+      <c r="E65" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F65" s="33" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
-      <c r="A66" s="31" t="s">
+      <c r="A66" s="30" t="s">
         <v>583</v>
       </c>
-      <c r="B66" s="31" t="s">
+      <c r="B66" s="30" t="s">
         <v>638</v>
       </c>
-      <c r="C66" s="36">
+      <c r="C66" s="35">
         <v>46262.25</v>
       </c>
-      <c r="D66" s="36">
+      <c r="D66" s="35">
         <v>46262.423611111109</v>
       </c>
-      <c r="E66" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F66" s="34" t="s">
+      <c r="E66" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F66" s="33" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="35">
         <v>46262.427083333336</v>
       </c>
-      <c r="D67" s="36">
+      <c r="D67" s="35">
         <v>46262.534722222219</v>
       </c>
-      <c r="E67" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F67" s="33" t="s">
+      <c r="E67" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F67" s="32" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="B68" s="30" t="s">
+      <c r="B68" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="35">
         <v>46262.50277777778</v>
       </c>
-      <c r="D68" s="36">
+      <c r="D68" s="35">
         <v>46262.550694444442</v>
       </c>
-      <c r="E68" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F68" s="33" t="s">
+      <c r="E68" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F68" s="32" t="s">
         <v>614</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="B69" s="30" t="s">
+      <c r="B69" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="35">
         <v>46263.194444444445</v>
       </c>
-      <c r="D69" s="36">
+      <c r="D69" s="35">
         <v>46263.3125</v>
       </c>
-      <c r="E69" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F69" s="33" t="s">
+      <c r="E69" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F69" s="32" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15">
-      <c r="A70" s="30" t="s">
+      <c r="A70" s="29" t="s">
         <v>590</v>
       </c>
-      <c r="B70" s="30" t="s">
+      <c r="B70" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C70" s="36">
+      <c r="C70" s="35">
         <v>46263.739583333336</v>
       </c>
-      <c r="D70" s="36">
+      <c r="D70" s="35">
         <v>46266.666666666664</v>
       </c>
-      <c r="E70" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F70" s="34" t="s">
+      <c r="E70" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F70" s="33" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B71" s="30" t="s">
+      <c r="B71" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="C71" s="36">
+      <c r="C71" s="35">
         <v>46264.333333333336</v>
       </c>
-      <c r="D71" s="36">
+      <c r="D71" s="35">
         <v>46264.5</v>
       </c>
-      <c r="E71" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F71" s="34" t="s">
+      <c r="E71" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F71" s="33" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="29" t="s">
         <v>591</v>
       </c>
-      <c r="B72" s="30" t="s">
+      <c r="B72" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C72" s="36">
+      <c r="C72" s="35">
         <v>46264.708333333336</v>
       </c>
-      <c r="D72" s="36">
+      <c r="D72" s="35">
         <v>46264.315972222219</v>
       </c>
-      <c r="E72" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F72" s="34" t="s">
+      <c r="E72" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F72" s="33" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15">
-      <c r="A73" s="30" t="s">
+      <c r="A73" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="B73" s="30" t="s">
+      <c r="B73" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C73" s="36">
+      <c r="C73" s="35">
         <v>46265.25</v>
       </c>
-      <c r="D73" s="36">
+      <c r="D73" s="35">
         <v>46265.316666666666</v>
       </c>
-      <c r="E73" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F73" s="33" t="s">
+      <c r="E73" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F73" s="32" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15">
-      <c r="A74" s="30" t="s">
+      <c r="A74" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="30" t="s">
+      <c r="B74" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="C74" s="36">
+      <c r="C74" s="35">
         <v>46265.291666666664</v>
       </c>
-      <c r="D74" s="36">
+      <c r="D74" s="35">
         <v>46265.479166666664</v>
       </c>
-      <c r="E74" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F74" s="33" t="s">
+      <c r="E74" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F74" s="32" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15">
-      <c r="A75" s="30" t="s">
+      <c r="A75" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="30" t="s">
+      <c r="B75" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C75" s="36">
+      <c r="C75" s="35">
         <v>46265.569444444445</v>
       </c>
-      <c r="D75" s="36">
+      <c r="D75" s="35">
         <v>46265.701388888891</v>
       </c>
-      <c r="E75" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F75" s="33" t="s">
+      <c r="E75" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F75" s="32" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15">
-      <c r="A76" s="30" t="s">
+      <c r="A76" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C76" s="36">
+      <c r="C76" s="35">
         <v>46265.59375</v>
       </c>
-      <c r="D76" s="36">
+      <c r="D76" s="35">
         <v>46265.618055555555</v>
       </c>
-      <c r="E76" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F76" s="34" t="s">
+      <c r="E76" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F76" s="33" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15">
-      <c r="A77" s="33" t="s">
+      <c r="A77" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C77" s="36">
+      <c r="C77" s="35">
         <v>46265.631944444445</v>
       </c>
-      <c r="D77" s="36">
+      <c r="D77" s="35">
         <v>46265.692361111112</v>
       </c>
-      <c r="E77" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F77" s="33" t="s">
+      <c r="E77" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F77" s="32" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15">
-      <c r="A78" s="30" t="s">
+      <c r="A78" s="29" t="s">
         <v>583</v>
       </c>
-      <c r="B78" s="30" t="s">
+      <c r="B78" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="C78" s="36">
+      <c r="C78" s="35">
         <v>46265.69027777778</v>
       </c>
-      <c r="D78" s="36">
+      <c r="D78" s="35">
         <v>46265.693055555559</v>
       </c>
-      <c r="E78" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="F78" s="34" t="s">
+      <c r="E78" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="F78" s="33" t="s">
         <v>608</v>
       </c>
     </row>
@@ -13240,31 +14347,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PDF xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </PDF>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f2c58eb1-9d7f-4123-980d-e0326d949ea4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100129872B20EB72F43A65F017F96B1C226" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8918ff54d439e714c6ec094a8552ca51">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae836115-58a4-4701-a509-51b7f29d6ef2" xmlns:ns3="f2c58eb1-9d7f-4123-980d-e0326d949ea4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dac983c0446f866ea106b147c21f2a9" ns2:_="" ns3:_="">
     <xsd:import namespace="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
@@ -13524,32 +14606,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D474CDF3-F77E-4C91-BAE3-2259CB3B5596}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f2c58eb1-9d7f-4123-980d-e0326d949ea4"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PDF xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </PDF>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f2c58eb1-9d7f-4123-980d-e0326d949ea4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ae836115-58a4-4701-a509-51b7f29d6ef2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{479B8213-A263-4381-AC21-345AF9A36A7B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13566,4 +14648,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8CEBC78-8A27-481E-A7D3-01252DD5284A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D474CDF3-F77E-4C91-BAE3-2259CB3B5596}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="ae836115-58a4-4701-a509-51b7f29d6ef2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f2c58eb1-9d7f-4123-980d-e0326d949ea4"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>